--- a/research/traditional_assets/database/data/oman/oman_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_farming_agriculture.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09096967173351193</v>
+        <v>0.09087146722591165</v>
       </c>
       <c r="C2">
-        <v>40.36314440118233</v>
+        <v>40.02503095265016</v>
       </c>
       <c r="D2">
-        <v>39.14314440118233</v>
+        <v>39.18603095265016</v>
       </c>
       <c r="E2">
-        <v>-11.9</v>
+        <v>-11.519</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.381</v>
       </c>
       <c r="G2">
         <v>1.22</v>
@@ -1451,28 +1451,28 @@
         <v>5.88</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0191643</v>
       </c>
       <c r="N2">
-        <v>5.88</v>
+        <v>5.8608357</v>
       </c>
       <c r="O2">
-        <v>0.882</v>
+        <v>0.879125355</v>
       </c>
       <c r="P2">
-        <v>4.998</v>
+        <v>4.981710345</v>
       </c>
       <c r="Q2">
-        <v>6.748</v>
+        <v>6.731710345</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09096967173351193</v>
+        <v>0.09135749214738551</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5937668451279635</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>306.8204943566945</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09087146722591165</v>
+        <v>0.0907732627183114</v>
       </c>
       <c r="C3">
-        <v>40.02503095265016</v>
+        <v>39.68701158310352</v>
       </c>
       <c r="D3">
-        <v>39.18603095265016</v>
+        <v>39.22901158310352</v>
       </c>
       <c r="E3">
-        <v>-11.519</v>
+        <v>-11.138</v>
       </c>
       <c r="F3">
-        <v>0.381</v>
+        <v>0.762</v>
       </c>
       <c r="G3">
         <v>1.22</v>
@@ -1533,28 +1533,28 @@
         <v>5.88</v>
       </c>
       <c r="M3">
-        <v>0.0191643</v>
+        <v>0.0383286</v>
       </c>
       <c r="N3">
-        <v>5.8608357</v>
+        <v>5.8416714</v>
       </c>
       <c r="O3">
-        <v>0.879125355</v>
+        <v>0.87625071</v>
       </c>
       <c r="P3">
-        <v>4.981710345</v>
+        <v>4.96542069</v>
       </c>
       <c r="Q3">
-        <v>6.731710345</v>
+        <v>6.71542069</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09135749214738551</v>
+        <v>0.09175322726358306</v>
       </c>
       <c r="T3">
-        <v>0.5937668451279635</v>
+        <v>0.5989246003154262</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>306.8204943566945</v>
+        <v>153.4102471783472</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0907732627183114</v>
+        <v>0.09067505821071112</v>
       </c>
       <c r="C4">
-        <v>39.68701158310352</v>
+        <v>39.34908660244989</v>
       </c>
       <c r="D4">
-        <v>39.22901158310352</v>
+        <v>39.2720866024499</v>
       </c>
       <c r="E4">
-        <v>-11.138</v>
+        <v>-10.757</v>
       </c>
       <c r="F4">
-        <v>0.762</v>
+        <v>1.143</v>
       </c>
       <c r="G4">
         <v>1.22</v>
@@ -1615,28 +1615,28 @@
         <v>5.88</v>
       </c>
       <c r="M4">
-        <v>0.0383286</v>
+        <v>0.0574929</v>
       </c>
       <c r="N4">
-        <v>5.8416714</v>
+        <v>5.8225071</v>
       </c>
       <c r="O4">
-        <v>0.87625071</v>
+        <v>0.873376065</v>
       </c>
       <c r="P4">
-        <v>4.96542069</v>
+        <v>4.949131035000001</v>
       </c>
       <c r="Q4">
-        <v>6.71542069</v>
+        <v>6.699131035000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09175322726358306</v>
+        <v>0.0921571218667125</v>
       </c>
       <c r="T4">
-        <v>0.5989246003154262</v>
+        <v>0.6041887009706713</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>153.4102471783472</v>
+        <v>102.2734981188982</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09067505821071112</v>
+        <v>0.09057685370311085</v>
       </c>
       <c r="C5">
-        <v>39.34908660244989</v>
+        <v>39.01125632195936</v>
       </c>
       <c r="D5">
-        <v>39.2720866024499</v>
+        <v>39.31525632195936</v>
       </c>
       <c r="E5">
-        <v>-10.757</v>
+        <v>-10.376</v>
       </c>
       <c r="F5">
-        <v>1.143</v>
+        <v>1.524</v>
       </c>
       <c r="G5">
         <v>1.22</v>
@@ -1697,28 +1697,28 @@
         <v>5.88</v>
       </c>
       <c r="M5">
-        <v>0.0574929</v>
+        <v>0.07665719999999999</v>
       </c>
       <c r="N5">
-        <v>5.8225071</v>
+        <v>5.8033428</v>
       </c>
       <c r="O5">
-        <v>0.873376065</v>
+        <v>0.87050142</v>
       </c>
       <c r="P5">
-        <v>4.949131035000001</v>
+        <v>4.93284138</v>
       </c>
       <c r="Q5">
-        <v>6.699131035000001</v>
+        <v>6.68284138</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0921571218667125</v>
+        <v>0.09256943094074048</v>
       </c>
       <c r="T5">
-        <v>0.6041887009706713</v>
+        <v>0.6095624703895676</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>102.2734981188982</v>
+        <v>76.70512358917362</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09057685370311085</v>
+        <v>0.09047864919551057</v>
       </c>
       <c r="C6">
-        <v>39.01125632195936</v>
+        <v>38.67352105427215</v>
       </c>
       <c r="D6">
-        <v>39.31525632195936</v>
+        <v>39.35852105427215</v>
       </c>
       <c r="E6">
-        <v>-10.376</v>
+        <v>-9.995000000000001</v>
       </c>
       <c r="F6">
-        <v>1.524</v>
+        <v>1.905</v>
       </c>
       <c r="G6">
         <v>1.22</v>
@@ -1779,28 +1779,28 @@
         <v>5.88</v>
       </c>
       <c r="M6">
-        <v>0.07665719999999999</v>
+        <v>0.0958215</v>
       </c>
       <c r="N6">
-        <v>5.8033428</v>
+        <v>5.784178499999999</v>
       </c>
       <c r="O6">
-        <v>0.87050142</v>
+        <v>0.8676267749999999</v>
       </c>
       <c r="P6">
-        <v>4.93284138</v>
+        <v>4.916551725</v>
       </c>
       <c r="Q6">
-        <v>6.68284138</v>
+        <v>6.666551725</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09256943094074048</v>
+        <v>0.09299042020580062</v>
       </c>
       <c r="T6">
-        <v>0.6095624703895676</v>
+        <v>0.61504937179623</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>76.70512358917362</v>
+        <v>61.36409887133889</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09047864919551057</v>
+        <v>0.09038044468791033</v>
       </c>
       <c r="C7">
-        <v>38.67352105427215</v>
+        <v>38.33588111340624</v>
       </c>
       <c r="D7">
-        <v>39.35852105427215</v>
+        <v>39.40188111340624</v>
       </c>
       <c r="E7">
-        <v>-9.995000000000001</v>
+        <v>-9.614000000000001</v>
       </c>
       <c r="F7">
-        <v>1.905</v>
+        <v>2.286</v>
       </c>
       <c r="G7">
         <v>1.22</v>
@@ -1861,28 +1861,28 @@
         <v>5.88</v>
       </c>
       <c r="M7">
-        <v>0.0958215</v>
+        <v>0.1149858</v>
       </c>
       <c r="N7">
-        <v>5.784178499999999</v>
+        <v>5.7650142</v>
       </c>
       <c r="O7">
-        <v>0.8676267749999999</v>
+        <v>0.86475213</v>
       </c>
       <c r="P7">
-        <v>4.916551725</v>
+        <v>4.900262069999999</v>
       </c>
       <c r="Q7">
-        <v>6.666551725</v>
+        <v>6.650262069999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09299042020580062</v>
+        <v>0.0934203666892663</v>
       </c>
       <c r="T7">
-        <v>0.61504937179623</v>
+        <v>0.6206530157860128</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>61.36409887133889</v>
+        <v>51.13674905944907</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09038044468791032</v>
+        <v>0.09028224018031006</v>
       </c>
       <c r="C8">
-        <v>38.33588111340624</v>
+        <v>37.99833681476488</v>
       </c>
       <c r="D8">
-        <v>39.40188111340625</v>
+        <v>39.44533681476489</v>
       </c>
       <c r="E8">
-        <v>-9.614000000000001</v>
+        <v>-9.233000000000001</v>
       </c>
       <c r="F8">
-        <v>2.286</v>
+        <v>2.667</v>
       </c>
       <c r="G8">
         <v>1.22</v>
@@ -1943,28 +1943,28 @@
         <v>5.88</v>
       </c>
       <c r="M8">
-        <v>0.1149858</v>
+        <v>0.1341501</v>
       </c>
       <c r="N8">
-        <v>5.7650142</v>
+        <v>5.7458499</v>
       </c>
       <c r="O8">
-        <v>0.86475213</v>
+        <v>0.8618774849999999</v>
       </c>
       <c r="P8">
-        <v>4.900262069999999</v>
+        <v>4.883972415</v>
       </c>
       <c r="Q8">
-        <v>6.650262069999999</v>
+        <v>6.633972415</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0934203666892663</v>
+        <v>0.09385955933366671</v>
       </c>
       <c r="T8">
-        <v>0.6206530157860128</v>
+        <v>0.6263771682486943</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>51.13674905944907</v>
+        <v>43.8314991938135</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09028224018031004</v>
+        <v>0.0901840356727098</v>
       </c>
       <c r="C9">
-        <v>37.99833681476489</v>
+        <v>37.66088847514429</v>
       </c>
       <c r="D9">
-        <v>39.44533681476489</v>
+        <v>39.48888847514429</v>
       </c>
       <c r="E9">
-        <v>-9.233000000000001</v>
+        <v>-8.852</v>
       </c>
       <c r="F9">
-        <v>2.667</v>
+        <v>3.048</v>
       </c>
       <c r="G9">
         <v>1.22</v>
@@ -2025,28 +2025,28 @@
         <v>5.88</v>
       </c>
       <c r="M9">
-        <v>0.1341501</v>
+        <v>0.1533144</v>
       </c>
       <c r="N9">
-        <v>5.7458499</v>
+        <v>5.7266856</v>
       </c>
       <c r="O9">
-        <v>0.8618774849999999</v>
+        <v>0.8590028399999999</v>
       </c>
       <c r="P9">
-        <v>4.883972415</v>
+        <v>4.86768276</v>
       </c>
       <c r="Q9">
-        <v>6.633972415</v>
+        <v>6.61768276</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09385955933366671</v>
+        <v>0.09430829964424978</v>
       </c>
       <c r="T9">
-        <v>0.6263771682486943</v>
+        <v>0.6322257588083906</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>43.8314991938135</v>
+        <v>38.35256179458681</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0901840356727098</v>
+        <v>0.09008583116510953</v>
       </c>
       <c r="C10">
-        <v>37.66088847514429</v>
+        <v>37.3235364127413</v>
       </c>
       <c r="D10">
-        <v>39.48888847514429</v>
+        <v>39.53253641274131</v>
       </c>
       <c r="E10">
-        <v>-8.852</v>
+        <v>-8.471</v>
       </c>
       <c r="F10">
-        <v>3.048</v>
+        <v>3.429</v>
       </c>
       <c r="G10">
         <v>1.22</v>
@@ -2107,28 +2107,28 @@
         <v>5.88</v>
       </c>
       <c r="M10">
-        <v>0.1533144</v>
+        <v>0.1724787</v>
       </c>
       <c r="N10">
-        <v>5.7266856</v>
+        <v>5.7075213</v>
       </c>
       <c r="O10">
-        <v>0.8590028399999999</v>
+        <v>0.8561281949999999</v>
       </c>
       <c r="P10">
-        <v>4.86768276</v>
+        <v>4.851393105</v>
       </c>
       <c r="Q10">
-        <v>6.61768276</v>
+        <v>6.601393105</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09430829964424978</v>
+        <v>0.09476690237924124</v>
       </c>
       <c r="T10">
-        <v>0.6322257588083906</v>
+        <v>0.6382028898199483</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>38.35256179458681</v>
+        <v>34.09116603963272</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09008583116510953</v>
+        <v>0.08998762665750926</v>
       </c>
       <c r="C11">
-        <v>37.3235364127413</v>
+        <v>36.98628094716118</v>
       </c>
       <c r="D11">
-        <v>39.53253641274131</v>
+        <v>39.57628094716119</v>
       </c>
       <c r="E11">
-        <v>-8.471</v>
+        <v>-8.09</v>
       </c>
       <c r="F11">
-        <v>3.429</v>
+        <v>3.81</v>
       </c>
       <c r="G11">
         <v>1.22</v>
@@ -2189,28 +2189,28 @@
         <v>5.88</v>
       </c>
       <c r="M11">
-        <v>0.1724787</v>
+        <v>0.191643</v>
       </c>
       <c r="N11">
-        <v>5.7075213</v>
+        <v>5.688357</v>
       </c>
       <c r="O11">
-        <v>0.8561281949999999</v>
+        <v>0.8532535499999999</v>
       </c>
       <c r="P11">
-        <v>4.851393105</v>
+        <v>4.83510345</v>
       </c>
       <c r="Q11">
-        <v>6.601393105</v>
+        <v>6.58510345</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09476690237924124</v>
+        <v>0.0952356962861214</v>
       </c>
       <c r="T11">
-        <v>0.6382028898199483</v>
+        <v>0.6443128459650963</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>34.09116603963272</v>
+        <v>30.68204943566945</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08998762665750926</v>
+        <v>0.089889422149909</v>
       </c>
       <c r="C12">
-        <v>36.98628094716118</v>
+        <v>36.64912239942537</v>
       </c>
       <c r="D12">
-        <v>39.57628094716119</v>
+        <v>39.62012239942538</v>
       </c>
       <c r="E12">
-        <v>-8.09</v>
+        <v>-7.709000000000001</v>
       </c>
       <c r="F12">
-        <v>3.81</v>
+        <v>4.191</v>
       </c>
       <c r="G12">
         <v>1.22</v>
@@ -2271,28 +2271,28 @@
         <v>5.88</v>
       </c>
       <c r="M12">
-        <v>0.191643</v>
+        <v>0.2108073</v>
       </c>
       <c r="N12">
-        <v>5.688357</v>
+        <v>5.6691927</v>
       </c>
       <c r="O12">
-        <v>0.8532535499999999</v>
+        <v>0.850378905</v>
       </c>
       <c r="P12">
-        <v>4.83510345</v>
+        <v>4.818813795</v>
       </c>
       <c r="Q12">
-        <v>6.58510345</v>
+        <v>6.568813795</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0952356962861214</v>
+        <v>0.09571502488753819</v>
       </c>
       <c r="T12">
-        <v>0.6443128459650963</v>
+        <v>0.6505601044955284</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>30.68204943566944</v>
+        <v>27.89277221424496</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.089889422149909</v>
+        <v>0.08979121764230871</v>
       </c>
       <c r="C13">
-        <v>36.64912239942537</v>
+        <v>36.31206109197937</v>
       </c>
       <c r="D13">
-        <v>39.62012239942538</v>
+        <v>39.66406109197938</v>
       </c>
       <c r="E13">
-        <v>-7.709000000000001</v>
+        <v>-7.328</v>
       </c>
       <c r="F13">
-        <v>4.191</v>
+        <v>4.572</v>
       </c>
       <c r="G13">
         <v>1.22</v>
@@ -2353,28 +2353,28 @@
         <v>5.88</v>
       </c>
       <c r="M13">
-        <v>0.2108073</v>
+        <v>0.2299716</v>
       </c>
       <c r="N13">
-        <v>5.6691927</v>
+        <v>5.6500284</v>
       </c>
       <c r="O13">
-        <v>0.850378905</v>
+        <v>0.84750426</v>
       </c>
       <c r="P13">
-        <v>4.818813795</v>
+        <v>4.80252414</v>
       </c>
       <c r="Q13">
-        <v>6.568813795</v>
+        <v>6.55252414</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09571502488753819</v>
+        <v>0.09620524732080536</v>
       </c>
       <c r="T13">
-        <v>0.6505601044955284</v>
+        <v>0.6569493461743794</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>27.89277221424496</v>
+        <v>25.56837452972454</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08979121764230871</v>
+        <v>0.08969301313470844</v>
       </c>
       <c r="C14">
-        <v>36.31206109197937</v>
+        <v>35.97509734870063</v>
       </c>
       <c r="D14">
-        <v>39.66406109197938</v>
+        <v>39.70809734870063</v>
       </c>
       <c r="E14">
-        <v>-7.328</v>
+        <v>-6.947</v>
       </c>
       <c r="F14">
-        <v>4.572</v>
+        <v>4.953</v>
       </c>
       <c r="G14">
         <v>1.22</v>
@@ -2435,28 +2435,28 @@
         <v>5.88</v>
       </c>
       <c r="M14">
-        <v>0.2299716</v>
+        <v>0.2491359</v>
       </c>
       <c r="N14">
-        <v>5.6500284</v>
+        <v>5.6308641</v>
       </c>
       <c r="O14">
-        <v>0.84750426</v>
+        <v>0.844629615</v>
       </c>
       <c r="P14">
-        <v>4.80252414</v>
+        <v>4.786234485</v>
       </c>
       <c r="Q14">
-        <v>6.55252414</v>
+        <v>6.536234485</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09620524732080536</v>
+        <v>0.09670673923529706</v>
       </c>
       <c r="T14">
-        <v>0.6569493461743794</v>
+        <v>0.6634854669722844</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.56837452972454</v>
+        <v>23.6015764889765</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08969301313470844</v>
+        <v>0.08959480862710817</v>
       </c>
       <c r="C15">
-        <v>35.97509734870063</v>
+        <v>35.63823149490652</v>
       </c>
       <c r="D15">
-        <v>39.70809734870063</v>
+        <v>39.75223149490652</v>
       </c>
       <c r="E15">
-        <v>-6.947</v>
+        <v>-6.566</v>
       </c>
       <c r="F15">
-        <v>4.953</v>
+        <v>5.334000000000001</v>
       </c>
       <c r="G15">
         <v>1.22</v>
@@ -2517,28 +2517,28 @@
         <v>5.88</v>
       </c>
       <c r="M15">
-        <v>0.2491359</v>
+        <v>0.2683002</v>
       </c>
       <c r="N15">
-        <v>5.6308641</v>
+        <v>5.6116998</v>
       </c>
       <c r="O15">
-        <v>0.844629615</v>
+        <v>0.84175497</v>
       </c>
       <c r="P15">
-        <v>4.786234485</v>
+        <v>4.76994483</v>
       </c>
       <c r="Q15">
-        <v>6.536234485</v>
+        <v>6.51994483</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09670673923529706</v>
+        <v>0.09721989375245137</v>
       </c>
       <c r="T15">
-        <v>0.6634854669722844</v>
+        <v>0.670173590579443</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.6015764889765</v>
+        <v>21.91574959690675</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08959480862710817</v>
+        <v>0.08949660411950791</v>
       </c>
       <c r="C16">
-        <v>35.63823149490652</v>
+        <v>35.30146385736231</v>
       </c>
       <c r="D16">
-        <v>39.75223149490652</v>
+        <v>39.79646385736232</v>
       </c>
       <c r="E16">
-        <v>-6.566</v>
+        <v>-6.185</v>
       </c>
       <c r="F16">
-        <v>5.334000000000001</v>
+        <v>5.715000000000001</v>
       </c>
       <c r="G16">
         <v>1.22</v>
@@ -2599,28 +2599,28 @@
         <v>5.88</v>
       </c>
       <c r="M16">
-        <v>0.2683002</v>
+        <v>0.2874645</v>
       </c>
       <c r="N16">
-        <v>5.6116998</v>
+        <v>5.5925355</v>
       </c>
       <c r="O16">
-        <v>0.84175497</v>
+        <v>0.838880325</v>
       </c>
       <c r="P16">
-        <v>4.76994483</v>
+        <v>4.753655175</v>
       </c>
       <c r="Q16">
-        <v>6.51994483</v>
+        <v>6.503655175</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09721989375245137</v>
+        <v>0.09774512249353873</v>
       </c>
       <c r="T16">
-        <v>0.670173590579443</v>
+        <v>0.6770190818008879</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.91574959690675</v>
+        <v>20.45469962377963</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08949660411950791</v>
+        <v>0.08939839961190764</v>
       </c>
       <c r="C17">
-        <v>35.30146385736232</v>
+        <v>34.96479476428932</v>
       </c>
       <c r="D17">
-        <v>39.79646385736232</v>
+        <v>39.84079476428932</v>
       </c>
       <c r="E17">
-        <v>-6.185</v>
+        <v>-5.804</v>
       </c>
       <c r="F17">
-        <v>5.715</v>
+        <v>6.096</v>
       </c>
       <c r="G17">
         <v>1.22</v>
@@ -2681,28 +2681,28 @@
         <v>5.88</v>
       </c>
       <c r="M17">
-        <v>0.2874645</v>
+        <v>0.3066288</v>
       </c>
       <c r="N17">
-        <v>5.5925355</v>
+        <v>5.5733712</v>
       </c>
       <c r="O17">
-        <v>0.838880325</v>
+        <v>0.8360056799999999</v>
       </c>
       <c r="P17">
-        <v>4.753655175</v>
+        <v>4.73736552</v>
       </c>
       <c r="Q17">
-        <v>6.503655175</v>
+        <v>6.48736552</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09774512249353873</v>
+        <v>0.09828285668084244</v>
       </c>
       <c r="T17">
-        <v>0.6770190818008879</v>
+        <v>0.6840275609085577</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.45469962377964</v>
+        <v>19.17628089729341</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08939839961190764</v>
+        <v>0.08930019510430737</v>
       </c>
       <c r="C18">
-        <v>34.96479476428932</v>
+        <v>34.6282245453729</v>
       </c>
       <c r="D18">
-        <v>39.84079476428932</v>
+        <v>39.88522454537291</v>
       </c>
       <c r="E18">
-        <v>-5.804</v>
+        <v>-5.423</v>
       </c>
       <c r="F18">
-        <v>6.096</v>
+        <v>6.477</v>
       </c>
       <c r="G18">
         <v>1.22</v>
@@ -2763,28 +2763,28 @@
         <v>5.88</v>
       </c>
       <c r="M18">
-        <v>0.3066288</v>
+        <v>0.3257931</v>
       </c>
       <c r="N18">
-        <v>5.5733712</v>
+        <v>5.5542069</v>
       </c>
       <c r="O18">
-        <v>0.8360056799999999</v>
+        <v>0.833131035</v>
       </c>
       <c r="P18">
-        <v>4.73736552</v>
+        <v>4.721075865</v>
       </c>
       <c r="Q18">
-        <v>6.48736552</v>
+        <v>6.471075865</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09828285668084244</v>
+        <v>0.09883354831844263</v>
       </c>
       <c r="T18">
-        <v>0.6840275609085577</v>
+        <v>0.6912049190308698</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.17628089729341</v>
+        <v>18.0482643739232</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08930019510430737</v>
+        <v>0.08920199059670711</v>
       </c>
       <c r="C19">
-        <v>34.6282245453729</v>
+        <v>34.29175353177074</v>
       </c>
       <c r="D19">
-        <v>39.88522454537291</v>
+        <v>39.92975353177074</v>
       </c>
       <c r="E19">
-        <v>-5.423</v>
+        <v>-5.041999999999999</v>
       </c>
       <c r="F19">
-        <v>6.477</v>
+        <v>6.858000000000001</v>
       </c>
       <c r="G19">
         <v>1.22</v>
@@ -2845,28 +2845,28 @@
         <v>5.88</v>
       </c>
       <c r="M19">
-        <v>0.3257931</v>
+        <v>0.3449574000000001</v>
       </c>
       <c r="N19">
-        <v>5.5542069</v>
+        <v>5.5350426</v>
       </c>
       <c r="O19">
-        <v>0.833131035</v>
+        <v>0.83025639</v>
       </c>
       <c r="P19">
-        <v>4.721075865</v>
+        <v>4.70478621</v>
       </c>
       <c r="Q19">
-        <v>6.471075865</v>
+        <v>6.45478621</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09883354831844263</v>
+        <v>0.09939767145939891</v>
       </c>
       <c r="T19">
-        <v>0.6912049190308698</v>
+        <v>0.6985573346683605</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.0482643739232</v>
+        <v>17.04558301981636</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08920199059670711</v>
+        <v>0.08910378608910685</v>
       </c>
       <c r="C20">
-        <v>34.29175353177074</v>
+        <v>33.955382056121</v>
       </c>
       <c r="D20">
-        <v>39.92975353177074</v>
+        <v>39.974382056121</v>
       </c>
       <c r="E20">
-        <v>-5.042000000000001</v>
+        <v>-4.661</v>
       </c>
       <c r="F20">
-        <v>6.858</v>
+        <v>7.239000000000001</v>
       </c>
       <c r="G20">
         <v>1.22</v>
@@ -2927,28 +2927,28 @@
         <v>5.88</v>
       </c>
       <c r="M20">
-        <v>0.3449574</v>
+        <v>0.3641217</v>
       </c>
       <c r="N20">
-        <v>5.5350426</v>
+        <v>5.5158783</v>
       </c>
       <c r="O20">
-        <v>0.83025639</v>
+        <v>0.8273817449999999</v>
       </c>
       <c r="P20">
-        <v>4.70478621</v>
+        <v>4.688496555</v>
       </c>
       <c r="Q20">
-        <v>6.45478621</v>
+        <v>6.438496555</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09939767145939891</v>
+        <v>0.09997572356679857</v>
       </c>
       <c r="T20">
-        <v>0.6985573346683605</v>
+        <v>0.7060912914327027</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.04558301981636</v>
+        <v>16.14844707140497</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08910378608910685</v>
+        <v>0.08900558158150658</v>
       </c>
       <c r="C21">
-        <v>33.955382056121</v>
+        <v>33.61911045255066</v>
       </c>
       <c r="D21">
-        <v>39.974382056121</v>
+        <v>40.01911045255066</v>
       </c>
       <c r="E21">
-        <v>-4.661</v>
+        <v>-4.279999999999999</v>
       </c>
       <c r="F21">
-        <v>7.239000000000001</v>
+        <v>7.620000000000001</v>
       </c>
       <c r="G21">
         <v>1.22</v>
@@ -3009,28 +3009,28 @@
         <v>5.88</v>
       </c>
       <c r="M21">
-        <v>0.3641217</v>
+        <v>0.383286</v>
       </c>
       <c r="N21">
-        <v>5.5158783</v>
+        <v>5.496714</v>
       </c>
       <c r="O21">
-        <v>0.8273817449999999</v>
+        <v>0.8245070999999999</v>
       </c>
       <c r="P21">
-        <v>4.688496555</v>
+        <v>4.6722069</v>
       </c>
       <c r="Q21">
-        <v>6.438496555</v>
+        <v>6.4222069</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09997572356679857</v>
+        <v>0.1005682269768832</v>
       </c>
       <c r="T21">
-        <v>0.7060912914327027</v>
+        <v>0.7138135971161534</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.14844707140497</v>
+        <v>15.34102471783472</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08900558158150658</v>
+        <v>0.08890737707390632</v>
       </c>
       <c r="C22">
-        <v>33.61911045255066</v>
+        <v>33.2829390566838</v>
       </c>
       <c r="D22">
-        <v>40.01911045255066</v>
+        <v>40.06393905668381</v>
       </c>
       <c r="E22">
-        <v>-4.279999999999999</v>
+        <v>-3.898999999999999</v>
       </c>
       <c r="F22">
-        <v>7.620000000000001</v>
+        <v>8.001000000000001</v>
       </c>
       <c r="G22">
         <v>1.22</v>
@@ -3091,28 +3091,28 @@
         <v>5.88</v>
       </c>
       <c r="M22">
-        <v>0.383286</v>
+        <v>0.4024503</v>
       </c>
       <c r="N22">
-        <v>5.496714</v>
+        <v>5.4775497</v>
       </c>
       <c r="O22">
-        <v>0.8245070999999999</v>
+        <v>0.8216324549999999</v>
       </c>
       <c r="P22">
-        <v>4.6722069</v>
+        <v>4.655917245</v>
       </c>
       <c r="Q22">
-        <v>6.4222069</v>
+        <v>6.405917245</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1005682269768832</v>
+        <v>0.1011757304732991</v>
       </c>
       <c r="T22">
-        <v>0.7138135971161534</v>
+        <v>0.721731404209312</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.34102471783472</v>
+        <v>14.61049973127116</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08890737707390631</v>
+        <v>0.08880917256630605</v>
       </c>
       <c r="C23">
-        <v>33.28293905668382</v>
+        <v>32.94686820565006</v>
       </c>
       <c r="D23">
-        <v>40.06393905668381</v>
+        <v>40.10886820565006</v>
       </c>
       <c r="E23">
-        <v>-3.899000000000001</v>
+        <v>-3.518000000000001</v>
       </c>
       <c r="F23">
-        <v>8.000999999999999</v>
+        <v>8.382</v>
       </c>
       <c r="G23">
         <v>1.22</v>
@@ -3173,28 +3173,28 @@
         <v>5.88</v>
       </c>
       <c r="M23">
-        <v>0.4024502999999999</v>
+        <v>0.4216146</v>
       </c>
       <c r="N23">
-        <v>5.4775497</v>
+        <v>5.4583854</v>
       </c>
       <c r="O23">
-        <v>0.8216324549999999</v>
+        <v>0.81875781</v>
       </c>
       <c r="P23">
-        <v>4.655917245</v>
+        <v>4.63962759</v>
       </c>
       <c r="Q23">
-        <v>6.405917245</v>
+        <v>6.38962759</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1011757304732991</v>
+        <v>0.1017988109824436</v>
       </c>
       <c r="T23">
-        <v>0.7217314042093119</v>
+        <v>0.7298522319971668</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.61049973127117</v>
+        <v>13.94638610712248</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08880917256630605</v>
+        <v>0.08871096805870576</v>
       </c>
       <c r="C24">
-        <v>32.94686820565006</v>
+        <v>32.61089823809303</v>
       </c>
       <c r="D24">
-        <v>40.10886820565006</v>
+        <v>40.15389823809303</v>
       </c>
       <c r="E24">
-        <v>-3.518000000000001</v>
+        <v>-3.137</v>
       </c>
       <c r="F24">
-        <v>8.382</v>
+        <v>8.763</v>
       </c>
       <c r="G24">
         <v>1.22</v>
@@ -3255,28 +3255,28 @@
         <v>5.88</v>
       </c>
       <c r="M24">
-        <v>0.4216146</v>
+        <v>0.4407789</v>
       </c>
       <c r="N24">
-        <v>5.4583854</v>
+        <v>5.4392211</v>
       </c>
       <c r="O24">
-        <v>0.81875781</v>
+        <v>0.815883165</v>
       </c>
       <c r="P24">
-        <v>4.63962759</v>
+        <v>4.623337935</v>
       </c>
       <c r="Q24">
-        <v>6.38962759</v>
+        <v>6.373337935</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1017988109824436</v>
+        <v>0.1024380754009166</v>
       </c>
       <c r="T24">
-        <v>0.7298522319971668</v>
+        <v>0.7381839903769138</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>13.94638610712248</v>
+        <v>13.34002149376933</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08871096805870576</v>
+        <v>0.08891876355110549</v>
       </c>
       <c r="C25">
-        <v>32.61089823809303</v>
+        <v>32.13473618653336</v>
       </c>
       <c r="D25">
-        <v>40.15389823809303</v>
+        <v>40.05873618653336</v>
       </c>
       <c r="E25">
-        <v>-3.137</v>
+        <v>-2.755999999999998</v>
       </c>
       <c r="F25">
-        <v>8.763</v>
+        <v>9.144000000000002</v>
       </c>
       <c r="G25">
         <v>1.22</v>
@@ -3337,45 +3337,45 @@
         <v>5.88</v>
       </c>
       <c r="M25">
-        <v>0.4407789</v>
+        <v>0.4736592000000001</v>
       </c>
       <c r="N25">
-        <v>5.4392211</v>
+        <v>5.4063408</v>
       </c>
       <c r="O25">
-        <v>0.815883165</v>
+        <v>0.8109511199999999</v>
       </c>
       <c r="P25">
-        <v>4.623337935</v>
+        <v>4.59538968</v>
       </c>
       <c r="Q25">
-        <v>6.373337935</v>
+        <v>6.34538968</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1024380754009166</v>
+        <v>0.1030941625672441</v>
       </c>
       <c r="T25">
-        <v>0.7381839903769138</v>
+        <v>0.746735005556128</v>
       </c>
       <c r="U25">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.15</v>
       </c>
       <c r="W25">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>13.34002149376933</v>
+        <v>12.41398879194155</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08891876355110549</v>
+        <v>0.08883330904350524</v>
       </c>
       <c r="C26">
-        <v>32.13473618653336</v>
+        <v>31.79281628574718</v>
       </c>
       <c r="D26">
-        <v>40.05873618653336</v>
+        <v>40.09781628574718</v>
       </c>
       <c r="E26">
-        <v>-2.756</v>
+        <v>-2.375</v>
       </c>
       <c r="F26">
-        <v>9.144</v>
+        <v>9.525</v>
       </c>
       <c r="G26">
         <v>1.22</v>
@@ -3419,28 +3419,28 @@
         <v>5.88</v>
       </c>
       <c r="M26">
-        <v>0.4736592</v>
+        <v>0.493395</v>
       </c>
       <c r="N26">
-        <v>5.4063408</v>
+        <v>5.386604999999999</v>
       </c>
       <c r="O26">
-        <v>0.8109511199999999</v>
+        <v>0.8079907499999999</v>
       </c>
       <c r="P26">
-        <v>4.59538968</v>
+        <v>4.578614249999999</v>
       </c>
       <c r="Q26">
-        <v>6.34538968</v>
+        <v>6.328614249999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1030941625672441</v>
+        <v>0.1037677453913403</v>
       </c>
       <c r="T26">
-        <v>0.746735005556128</v>
+        <v>0.7555140478067879</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>12.41398879194155</v>
+        <v>11.91742924026388</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08883330904350524</v>
+        <v>0.08874785453590497</v>
       </c>
       <c r="C27">
-        <v>31.79281628574718</v>
+        <v>31.45097271016235</v>
       </c>
       <c r="D27">
-        <v>40.09781628574718</v>
+        <v>40.13697271016235</v>
       </c>
       <c r="E27">
-        <v>-2.375</v>
+        <v>-1.994</v>
       </c>
       <c r="F27">
-        <v>9.525</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="G27">
         <v>1.22</v>
@@ -3501,28 +3501,28 @@
         <v>5.88</v>
       </c>
       <c r="M27">
-        <v>0.493395</v>
+        <v>0.5131308</v>
       </c>
       <c r="N27">
-        <v>5.386604999999999</v>
+        <v>5.3668692</v>
       </c>
       <c r="O27">
-        <v>0.8079907499999999</v>
+        <v>0.8050303799999999</v>
       </c>
       <c r="P27">
-        <v>4.578614249999999</v>
+        <v>4.56183882</v>
       </c>
       <c r="Q27">
-        <v>6.328614249999999</v>
+        <v>6.31183882</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1037677453913403</v>
+        <v>0.1044595331566283</v>
       </c>
       <c r="T27">
-        <v>0.7555140478067879</v>
+        <v>0.7645303614696278</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.91742924026388</v>
+        <v>11.45906657717681</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08874785453590497</v>
+        <v>0.08866240002830469</v>
       </c>
       <c r="C28">
-        <v>31.45097271016235</v>
+        <v>31.10920568359733</v>
       </c>
       <c r="D28">
-        <v>40.13697271016235</v>
+        <v>40.17620568359733</v>
       </c>
       <c r="E28">
-        <v>-1.994</v>
+        <v>-1.613</v>
       </c>
       <c r="F28">
-        <v>9.906000000000001</v>
+        <v>10.287</v>
       </c>
       <c r="G28">
         <v>1.22</v>
@@ -3583,28 +3583,28 @@
         <v>5.88</v>
       </c>
       <c r="M28">
-        <v>0.5131308</v>
+        <v>0.5328666000000001</v>
       </c>
       <c r="N28">
-        <v>5.3668692</v>
+        <v>5.3471334</v>
       </c>
       <c r="O28">
-        <v>0.8050303799999999</v>
+        <v>0.8020700099999999</v>
       </c>
       <c r="P28">
-        <v>4.56183882</v>
+        <v>4.54506339</v>
       </c>
       <c r="Q28">
-        <v>6.31183882</v>
+        <v>6.29506339</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1044595331566283</v>
+        <v>0.1051702740113763</v>
       </c>
       <c r="T28">
-        <v>0.7645303614696278</v>
+        <v>0.7737936974246004</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.45906657717681</v>
+        <v>11.03465670394804</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08866240002830469</v>
+        <v>0.08857694552070444</v>
       </c>
       <c r="C29">
-        <v>31.10920568359733</v>
+        <v>30.76751543074644</v>
       </c>
       <c r="D29">
-        <v>40.17620568359733</v>
+        <v>40.21551543074644</v>
       </c>
       <c r="E29">
-        <v>-1.613</v>
+        <v>-1.231999999999999</v>
       </c>
       <c r="F29">
-        <v>10.287</v>
+        <v>10.668</v>
       </c>
       <c r="G29">
         <v>1.22</v>
@@ -3665,28 +3665,28 @@
         <v>5.88</v>
       </c>
       <c r="M29">
-        <v>0.5328666000000001</v>
+        <v>0.5526024</v>
       </c>
       <c r="N29">
-        <v>5.3471334</v>
+        <v>5.327397599999999</v>
       </c>
       <c r="O29">
-        <v>0.8020700099999999</v>
+        <v>0.7991096399999998</v>
       </c>
       <c r="P29">
-        <v>4.54506339</v>
+        <v>4.528287959999999</v>
       </c>
       <c r="Q29">
-        <v>6.29506339</v>
+        <v>6.278287959999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1051702740113763</v>
+        <v>0.1059007576676451</v>
       </c>
       <c r="T29">
-        <v>0.7737936974246004</v>
+        <v>0.783314348267211</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.03465670394804</v>
+        <v>10.64056182166418</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08857694552070444</v>
+        <v>0.08849149101310416</v>
       </c>
       <c r="C30">
-        <v>30.76751543074644</v>
+        <v>30.42590217718437</v>
       </c>
       <c r="D30">
-        <v>40.21551543074644</v>
+        <v>40.25490217718437</v>
       </c>
       <c r="E30">
-        <v>-1.231999999999999</v>
+        <v>-0.8509999999999991</v>
       </c>
       <c r="F30">
-        <v>10.668</v>
+        <v>11.049</v>
       </c>
       <c r="G30">
         <v>1.22</v>
@@ -3747,28 +3747,28 @@
         <v>5.88</v>
       </c>
       <c r="M30">
-        <v>0.5526024</v>
+        <v>0.5723382</v>
       </c>
       <c r="N30">
-        <v>5.327397599999999</v>
+        <v>5.3076618</v>
       </c>
       <c r="O30">
-        <v>0.7991096399999998</v>
+        <v>0.79614927</v>
       </c>
       <c r="P30">
-        <v>4.528287959999999</v>
+        <v>4.51151253</v>
       </c>
       <c r="Q30">
-        <v>6.278287959999999</v>
+        <v>6.26151253</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1059007576676451</v>
+        <v>0.1066518183283157</v>
       </c>
       <c r="T30">
-        <v>0.783314348267211</v>
+        <v>0.7931031864575007</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.64056182166418</v>
+        <v>10.27364589677921</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08849149101310415</v>
+        <v>0.0884060365055039</v>
       </c>
       <c r="C31">
-        <v>30.42590217718438</v>
+        <v>30.08436614937031</v>
       </c>
       <c r="D31">
-        <v>40.25490217718438</v>
+        <v>40.29436614937031</v>
       </c>
       <c r="E31">
-        <v>-0.8510000000000009</v>
+        <v>-0.4700000000000006</v>
       </c>
       <c r="F31">
-        <v>11.049</v>
+        <v>11.43</v>
       </c>
       <c r="G31">
         <v>1.22</v>
@@ -3829,28 +3829,28 @@
         <v>5.88</v>
       </c>
       <c r="M31">
-        <v>0.5723381999999999</v>
+        <v>0.592074</v>
       </c>
       <c r="N31">
-        <v>5.3076618</v>
+        <v>5.287926</v>
       </c>
       <c r="O31">
-        <v>0.79614927</v>
+        <v>0.7931889</v>
       </c>
       <c r="P31">
-        <v>4.51151253</v>
+        <v>4.4947371</v>
       </c>
       <c r="Q31">
-        <v>6.26151253</v>
+        <v>6.2447371</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1066518183283157</v>
+        <v>0.1074243378650056</v>
       </c>
       <c r="T31">
-        <v>0.7931031864575007</v>
+        <v>0.8031717057389416</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.27364589677921</v>
+        <v>9.931191033553239</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0884060365055039</v>
+        <v>0.08876853199790363</v>
       </c>
       <c r="C32">
-        <v>30.08436614937031</v>
+        <v>29.53649100237707</v>
       </c>
       <c r="D32">
-        <v>40.29436614937031</v>
+        <v>40.12749100237707</v>
       </c>
       <c r="E32">
-        <v>-0.4700000000000006</v>
+        <v>-0.08900000000000041</v>
       </c>
       <c r="F32">
-        <v>11.43</v>
+        <v>11.811</v>
       </c>
       <c r="G32">
         <v>1.22</v>
@@ -3911,45 +3911,45 @@
         <v>5.88</v>
       </c>
       <c r="M32">
-        <v>0.592074</v>
+        <v>0.6318885</v>
       </c>
       <c r="N32">
-        <v>5.287926</v>
+        <v>5.2481115</v>
       </c>
       <c r="O32">
-        <v>0.7931889</v>
+        <v>0.7872167250000001</v>
       </c>
       <c r="P32">
-        <v>4.4947371</v>
+        <v>4.460894775</v>
       </c>
       <c r="Q32">
-        <v>6.2447371</v>
+        <v>6.210894775</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1074243378650056</v>
+        <v>0.1082192492723241</v>
       </c>
       <c r="T32">
-        <v>0.8031717057389416</v>
+        <v>0.813532066158975</v>
       </c>
       <c r="U32">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.15</v>
       </c>
       <c r="W32">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>9.931191033553239</v>
+        <v>9.305439171626007</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08876853199790363</v>
+        <v>0.08869752749030335</v>
       </c>
       <c r="C33">
-        <v>29.53649100237707</v>
+        <v>29.18806905295131</v>
       </c>
       <c r="D33">
-        <v>40.12749100237707</v>
+        <v>40.16006905295131</v>
       </c>
       <c r="E33">
-        <v>-0.08900000000000041</v>
+        <v>0.2919999999999998</v>
       </c>
       <c r="F33">
-        <v>11.811</v>
+        <v>12.192</v>
       </c>
       <c r="G33">
         <v>1.22</v>
@@ -3993,28 +3993,28 @@
         <v>5.88</v>
       </c>
       <c r="M33">
-        <v>0.6318885</v>
+        <v>0.652272</v>
       </c>
       <c r="N33">
-        <v>5.2481115</v>
+        <v>5.227728</v>
       </c>
       <c r="O33">
-        <v>0.7872167250000001</v>
+        <v>0.7841591999999999</v>
       </c>
       <c r="P33">
-        <v>4.460894775</v>
+        <v>4.4435688</v>
       </c>
       <c r="Q33">
-        <v>6.210894775</v>
+        <v>6.1935688</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1082192492723241</v>
+        <v>0.1090375404269167</v>
       </c>
       <c r="T33">
-        <v>0.813532066158975</v>
+        <v>0.8241971430619505</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.305439171626007</v>
+        <v>9.014644197512695</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08869752749030335</v>
+        <v>0.0886265229827031</v>
       </c>
       <c r="C34">
-        <v>29.18806905295131</v>
+        <v>28.83970004437518</v>
       </c>
       <c r="D34">
-        <v>40.16006905295131</v>
+        <v>40.19270004437519</v>
       </c>
       <c r="E34">
-        <v>0.2919999999999998</v>
+        <v>0.673</v>
       </c>
       <c r="F34">
-        <v>12.192</v>
+        <v>12.573</v>
       </c>
       <c r="G34">
         <v>1.22</v>
@@ -4075,28 +4075,28 @@
         <v>5.88</v>
       </c>
       <c r="M34">
-        <v>0.652272</v>
+        <v>0.6726555</v>
       </c>
       <c r="N34">
-        <v>5.227728</v>
+        <v>5.2073445</v>
       </c>
       <c r="O34">
-        <v>0.7841591999999999</v>
+        <v>0.7811016749999999</v>
       </c>
       <c r="P34">
-        <v>4.4435688</v>
+        <v>4.426242824999999</v>
       </c>
       <c r="Q34">
-        <v>6.1935688</v>
+        <v>6.176242824999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1090375404269167</v>
+        <v>0.109880258183139</v>
       </c>
       <c r="T34">
-        <v>0.8241971430619505</v>
+        <v>0.8351805804694925</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.014644197512695</v>
+        <v>8.74147316122443</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0886265229827031</v>
+        <v>0.08855551847510282</v>
       </c>
       <c r="C35">
-        <v>28.83970004437518</v>
+        <v>28.49138410580068</v>
       </c>
       <c r="D35">
-        <v>40.19270004437519</v>
+        <v>40.22538410580069</v>
       </c>
       <c r="E35">
-        <v>0.673</v>
+        <v>1.054</v>
       </c>
       <c r="F35">
-        <v>12.573</v>
+        <v>12.954</v>
       </c>
       <c r="G35">
         <v>1.22</v>
@@ -4157,28 +4157,28 @@
         <v>5.88</v>
       </c>
       <c r="M35">
-        <v>0.6726555</v>
+        <v>0.6930390000000001</v>
       </c>
       <c r="N35">
-        <v>5.2073445</v>
+        <v>5.186961</v>
       </c>
       <c r="O35">
-        <v>0.7811016749999999</v>
+        <v>0.77804415</v>
       </c>
       <c r="P35">
-        <v>4.426242824999999</v>
+        <v>4.40891685</v>
       </c>
       <c r="Q35">
-        <v>6.176242824999999</v>
+        <v>6.15891685</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.109880258183139</v>
+        <v>0.1107485128410649</v>
       </c>
       <c r="T35">
-        <v>0.8351805804694925</v>
+        <v>0.8464968493136267</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.74147316122443</v>
+        <v>8.484371009423711</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08855551847510282</v>
+        <v>0.08848451396750254</v>
       </c>
       <c r="C36">
-        <v>28.49138410580068</v>
+        <v>28.14312136680019</v>
       </c>
       <c r="D36">
-        <v>40.22538410580069</v>
+        <v>40.2581213668002</v>
       </c>
       <c r="E36">
-        <v>1.054</v>
+        <v>1.435000000000002</v>
       </c>
       <c r="F36">
-        <v>12.954</v>
+        <v>13.335</v>
       </c>
       <c r="G36">
         <v>1.22</v>
@@ -4239,28 +4239,28 @@
         <v>5.88</v>
       </c>
       <c r="M36">
-        <v>0.6930390000000001</v>
+        <v>0.7134225000000002</v>
       </c>
       <c r="N36">
-        <v>5.186961</v>
+        <v>5.1665775</v>
       </c>
       <c r="O36">
-        <v>0.77804415</v>
+        <v>0.7749866249999999</v>
       </c>
       <c r="P36">
-        <v>4.40891685</v>
+        <v>4.391590875</v>
       </c>
       <c r="Q36">
-        <v>6.15891685</v>
+        <v>6.141590875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1107485128410649</v>
+        <v>0.111643483026927</v>
       </c>
       <c r="T36">
-        <v>0.8464968493136267</v>
+        <v>0.8581613110452727</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.484371009423711</v>
+        <v>8.241960409154462</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08848451396750254</v>
+        <v>0.08841350945990227</v>
       </c>
       <c r="C37">
-        <v>28.14312136680019</v>
+        <v>27.79491195736825</v>
       </c>
       <c r="D37">
-        <v>40.2581213668002</v>
+        <v>40.29091195736825</v>
       </c>
       <c r="E37">
-        <v>1.435000000000002</v>
+        <v>1.816000000000003</v>
       </c>
       <c r="F37">
-        <v>13.335</v>
+        <v>13.716</v>
       </c>
       <c r="G37">
         <v>1.22</v>
@@ -4321,28 +4321,28 @@
         <v>5.88</v>
       </c>
       <c r="M37">
-        <v>0.7134225000000002</v>
+        <v>0.7338060000000002</v>
       </c>
       <c r="N37">
-        <v>5.1665775</v>
+        <v>5.146193999999999</v>
       </c>
       <c r="O37">
-        <v>0.7749866249999999</v>
+        <v>0.7719290999999999</v>
       </c>
       <c r="P37">
-        <v>4.391590875</v>
+        <v>4.3742649</v>
       </c>
       <c r="Q37">
-        <v>6.141590875</v>
+        <v>6.1242649</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.111643483026927</v>
+        <v>0.1125664210310973</v>
       </c>
       <c r="T37">
-        <v>0.8581613110452727</v>
+        <v>0.8701902872060326</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.241960409154462</v>
+        <v>8.013017064455726</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08841350945990228</v>
+        <v>0.08834250495230203</v>
       </c>
       <c r="C38">
-        <v>27.79491195736825</v>
+        <v>27.44675600792329</v>
       </c>
       <c r="D38">
-        <v>40.29091195736825</v>
+        <v>40.32375600792329</v>
       </c>
       <c r="E38">
-        <v>1.815999999999999</v>
+        <v>2.196999999999999</v>
       </c>
       <c r="F38">
-        <v>13.716</v>
+        <v>14.097</v>
       </c>
       <c r="G38">
         <v>1.22</v>
@@ -4403,28 +4403,28 @@
         <v>5.88</v>
       </c>
       <c r="M38">
-        <v>0.733806</v>
+        <v>0.7541895</v>
       </c>
       <c r="N38">
-        <v>5.146193999999999</v>
+        <v>5.1258105</v>
       </c>
       <c r="O38">
-        <v>0.7719290999999999</v>
+        <v>0.768871575</v>
       </c>
       <c r="P38">
-        <v>4.3742649</v>
+        <v>4.356938925</v>
       </c>
       <c r="Q38">
-        <v>6.1242649</v>
+        <v>6.106938925</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1125664210310973</v>
+        <v>0.1135186586544477</v>
       </c>
       <c r="T38">
-        <v>0.8701902872060325</v>
+        <v>0.8826011356258642</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.013017064455727</v>
+        <v>7.796449035686654</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08834250495230203</v>
+        <v>0.08852990044470174</v>
       </c>
       <c r="C39">
-        <v>27.44675600792329</v>
+        <v>26.9791893857359</v>
       </c>
       <c r="D39">
-        <v>40.32375600792329</v>
+        <v>40.2371893857359</v>
       </c>
       <c r="E39">
-        <v>2.196999999999999</v>
+        <v>2.578000000000001</v>
       </c>
       <c r="F39">
-        <v>14.097</v>
+        <v>14.478</v>
       </c>
       <c r="G39">
         <v>1.22</v>
@@ -4485,45 +4485,45 @@
         <v>5.88</v>
       </c>
       <c r="M39">
-        <v>0.7541895</v>
+        <v>0.7861554000000001</v>
       </c>
       <c r="N39">
-        <v>5.1258105</v>
+        <v>5.0938446</v>
       </c>
       <c r="O39">
-        <v>0.768871575</v>
+        <v>0.7640766899999999</v>
       </c>
       <c r="P39">
-        <v>4.356938925</v>
+        <v>4.32976791</v>
       </c>
       <c r="Q39">
-        <v>6.106938925</v>
+        <v>6.07976791</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1135186586544477</v>
+        <v>0.1145016136204867</v>
       </c>
       <c r="T39">
-        <v>0.8826011356258642</v>
+        <v>0.8954123339947228</v>
       </c>
       <c r="U39">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V39">
         <v>0.15</v>
       </c>
       <c r="W39">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y39">
-        <v>7.796449035686654</v>
+        <v>7.479437271562339</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08852990044470174</v>
+        <v>0.08846569593710148</v>
       </c>
       <c r="C40">
-        <v>26.9791893857359</v>
+        <v>26.62780652182577</v>
       </c>
       <c r="D40">
-        <v>40.2371893857359</v>
+        <v>40.26680652182577</v>
       </c>
       <c r="E40">
-        <v>2.578000000000001</v>
+        <v>2.959000000000001</v>
       </c>
       <c r="F40">
-        <v>14.478</v>
+        <v>14.859</v>
       </c>
       <c r="G40">
         <v>1.22</v>
@@ -4567,28 +4567,28 @@
         <v>5.88</v>
       </c>
       <c r="M40">
-        <v>0.7861554000000001</v>
+        <v>0.8068437000000002</v>
       </c>
       <c r="N40">
-        <v>5.0938446</v>
+        <v>5.0731563</v>
       </c>
       <c r="O40">
-        <v>0.7640766899999999</v>
+        <v>0.760973445</v>
       </c>
       <c r="P40">
-        <v>4.32976791</v>
+        <v>4.312182855</v>
       </c>
       <c r="Q40">
-        <v>6.07976791</v>
+        <v>6.062182855</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1145016136204867</v>
+        <v>0.1155167966181991</v>
       </c>
       <c r="T40">
-        <v>0.8954123339947228</v>
+        <v>0.9086435716543634</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.479437271562339</v>
+        <v>7.287656828701766</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08846569593710148</v>
+        <v>0.08840149142950122</v>
       </c>
       <c r="C41">
-        <v>26.62780652182577</v>
+        <v>26.2764672902317</v>
       </c>
       <c r="D41">
-        <v>40.26680652182577</v>
+        <v>40.2964672902317</v>
       </c>
       <c r="E41">
-        <v>2.959000000000001</v>
+        <v>3.340000000000002</v>
       </c>
       <c r="F41">
-        <v>14.859</v>
+        <v>15.24</v>
       </c>
       <c r="G41">
         <v>1.22</v>
@@ -4649,28 +4649,28 @@
         <v>5.88</v>
       </c>
       <c r="M41">
-        <v>0.8068437000000002</v>
+        <v>0.8275320000000002</v>
       </c>
       <c r="N41">
-        <v>5.0731563</v>
+        <v>5.052467999999999</v>
       </c>
       <c r="O41">
-        <v>0.760973445</v>
+        <v>0.7578701999999998</v>
       </c>
       <c r="P41">
-        <v>4.312182855</v>
+        <v>4.294597799999999</v>
       </c>
       <c r="Q41">
-        <v>6.062182855</v>
+        <v>6.044597799999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1155167966181991</v>
+        <v>0.1165658190491687</v>
       </c>
       <c r="T41">
-        <v>0.9086435716543634</v>
+        <v>0.9223158505693256</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.287656828701766</v>
+        <v>7.105465407984221</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08840149142950122</v>
+        <v>0.08833728692190093</v>
       </c>
       <c r="C42">
-        <v>26.2764672902317</v>
+        <v>25.92517178744425</v>
       </c>
       <c r="D42">
-        <v>40.2964672902317</v>
+        <v>40.32617178744425</v>
       </c>
       <c r="E42">
-        <v>3.340000000000002</v>
+        <v>3.721000000000002</v>
       </c>
       <c r="F42">
-        <v>15.24</v>
+        <v>15.621</v>
       </c>
       <c r="G42">
         <v>1.22</v>
@@ -4731,28 +4731,28 @@
         <v>5.88</v>
       </c>
       <c r="M42">
-        <v>0.8275320000000002</v>
+        <v>0.8482203000000001</v>
       </c>
       <c r="N42">
-        <v>5.052467999999999</v>
+        <v>5.0317797</v>
       </c>
       <c r="O42">
-        <v>0.7578701999999998</v>
+        <v>0.7547669549999999</v>
       </c>
       <c r="P42">
-        <v>4.294597799999999</v>
+        <v>4.277012745</v>
       </c>
       <c r="Q42">
-        <v>6.044597799999999</v>
+        <v>6.027012745</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1165658190491687</v>
+        <v>0.117650401562544</v>
       </c>
       <c r="T42">
-        <v>0.9223158505693256</v>
+        <v>0.9364515965661508</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.105465407984221</v>
+        <v>6.932161373643143</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08833728692190093</v>
+        <v>0.08827308241430068</v>
       </c>
       <c r="C43">
-        <v>25.92517178744425</v>
+        <v>25.57392011023865</v>
       </c>
       <c r="D43">
-        <v>40.32617178744425</v>
+        <v>40.35592011023865</v>
       </c>
       <c r="E43">
-        <v>3.721000000000002</v>
+        <v>4.102000000000002</v>
       </c>
       <c r="F43">
-        <v>15.621</v>
+        <v>16.002</v>
       </c>
       <c r="G43">
         <v>1.22</v>
@@ -4813,28 +4813,28 @@
         <v>5.88</v>
       </c>
       <c r="M43">
-        <v>0.8482203000000001</v>
+        <v>0.8689086000000001</v>
       </c>
       <c r="N43">
-        <v>5.0317797</v>
+        <v>5.0110914</v>
       </c>
       <c r="O43">
-        <v>0.7547669549999999</v>
+        <v>0.75166371</v>
       </c>
       <c r="P43">
-        <v>4.277012745</v>
+        <v>4.25942769</v>
       </c>
       <c r="Q43">
-        <v>6.027012745</v>
+        <v>6.00942769</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.117650401562544</v>
+        <v>0.1187723834729322</v>
       </c>
       <c r="T43">
-        <v>0.9364515965661508</v>
+        <v>0.951074782080108</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.932161373643143</v>
+        <v>6.767109912365926</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08827308241430069</v>
+        <v>0.08820887790670043</v>
       </c>
       <c r="C44">
-        <v>25.57392011023865</v>
+        <v>25.22271235567596</v>
       </c>
       <c r="D44">
-        <v>40.35592011023865</v>
+        <v>40.38571235567596</v>
       </c>
       <c r="E44">
-        <v>4.101999999999999</v>
+        <v>4.482999999999999</v>
       </c>
       <c r="F44">
-        <v>16.002</v>
+        <v>16.383</v>
       </c>
       <c r="G44">
         <v>1.22</v>
@@ -4895,28 +4895,28 @@
         <v>5.88</v>
       </c>
       <c r="M44">
-        <v>0.8689085999999999</v>
+        <v>0.8895969</v>
       </c>
       <c r="N44">
-        <v>5.0110914</v>
+        <v>4.9904031</v>
       </c>
       <c r="O44">
-        <v>0.75166371</v>
+        <v>0.748560465</v>
       </c>
       <c r="P44">
-        <v>4.25942769</v>
+        <v>4.241842635</v>
       </c>
       <c r="Q44">
-        <v>6.00942769</v>
+        <v>5.991842635</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1187723834729322</v>
+        <v>0.1199337331696498</v>
       </c>
       <c r="T44">
-        <v>0.9510747820801078</v>
+        <v>0.9662110618226248</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.767109912365927</v>
+        <v>6.609735263241138</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08820887790670043</v>
+        <v>0.08814467339910015</v>
       </c>
       <c r="C45">
-        <v>25.22271235567596</v>
+        <v>24.87154862110404</v>
       </c>
       <c r="D45">
-        <v>40.38571235567596</v>
+        <v>40.41554862110404</v>
       </c>
       <c r="E45">
-        <v>4.482999999999999</v>
+        <v>4.863999999999999</v>
       </c>
       <c r="F45">
-        <v>16.383</v>
+        <v>16.764</v>
       </c>
       <c r="G45">
         <v>1.22</v>
@@ -4977,28 +4977,28 @@
         <v>5.88</v>
       </c>
       <c r="M45">
-        <v>0.8895969</v>
+        <v>0.9102852</v>
       </c>
       <c r="N45">
-        <v>4.9904031</v>
+        <v>4.9697148</v>
       </c>
       <c r="O45">
-        <v>0.748560465</v>
+        <v>0.74545722</v>
       </c>
       <c r="P45">
-        <v>4.241842635</v>
+        <v>4.22425758</v>
       </c>
       <c r="Q45">
-        <v>5.991842635</v>
+        <v>5.97425758</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1199337331696498</v>
+        <v>0.1211365596412503</v>
       </c>
       <c r="T45">
-        <v>0.9662110618226248</v>
+        <v>0.9818879229845174</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.609735263241138</v>
+        <v>6.459514007258385</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08814467339910015</v>
+        <v>0.08808046889149988</v>
       </c>
       <c r="C46">
-        <v>24.87154862110404</v>
+        <v>24.52042900415865</v>
       </c>
       <c r="D46">
-        <v>40.41554862110404</v>
+        <v>40.44542900415865</v>
       </c>
       <c r="E46">
-        <v>4.863999999999999</v>
+        <v>5.244999999999999</v>
       </c>
       <c r="F46">
-        <v>16.764</v>
+        <v>17.145</v>
       </c>
       <c r="G46">
         <v>1.22</v>
@@ -5059,28 +5059,28 @@
         <v>5.88</v>
       </c>
       <c r="M46">
-        <v>0.9102852</v>
+        <v>0.9309735</v>
       </c>
       <c r="N46">
-        <v>4.9697148</v>
+        <v>4.9490265</v>
       </c>
       <c r="O46">
-        <v>0.74545722</v>
+        <v>0.7423539749999999</v>
       </c>
       <c r="P46">
-        <v>4.22425758</v>
+        <v>4.206672525</v>
       </c>
       <c r="Q46">
-        <v>5.97425758</v>
+        <v>5.956672525</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1211365596412503</v>
+        <v>0.1223831252572725</v>
       </c>
       <c r="T46">
-        <v>0.9818879229845174</v>
+        <v>0.9981348518250244</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.459514007258385</v>
+        <v>6.315969251541531</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08808046889149988</v>
+        <v>0.08801626438389962</v>
       </c>
       <c r="C47">
-        <v>24.52042900415865</v>
+        <v>24.16935360276447</v>
       </c>
       <c r="D47">
-        <v>40.44542900415865</v>
+        <v>40.47535360276447</v>
       </c>
       <c r="E47">
-        <v>5.244999999999999</v>
+        <v>5.625999999999999</v>
       </c>
       <c r="F47">
-        <v>17.145</v>
+        <v>17.526</v>
       </c>
       <c r="G47">
         <v>1.22</v>
@@ -5141,28 +5141,28 @@
         <v>5.88</v>
       </c>
       <c r="M47">
-        <v>0.9309735</v>
+        <v>0.9516618</v>
       </c>
       <c r="N47">
-        <v>4.9490265</v>
+        <v>4.9283382</v>
       </c>
       <c r="O47">
-        <v>0.7423539749999999</v>
+        <v>0.73925073</v>
       </c>
       <c r="P47">
-        <v>4.206672525</v>
+        <v>4.18908747</v>
       </c>
       <c r="Q47">
-        <v>5.956672525</v>
+        <v>5.93908747</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1223831252572725</v>
+        <v>0.1236758599701845</v>
       </c>
       <c r="T47">
-        <v>0.9981348518250244</v>
+        <v>1.014983518770735</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.315969251541531</v>
+        <v>6.178665572160194</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08801626438389962</v>
+        <v>0.08835155987629933</v>
       </c>
       <c r="C48">
-        <v>24.16935360276447</v>
+        <v>23.63256455746756</v>
       </c>
       <c r="D48">
-        <v>40.47535360276447</v>
+        <v>40.31956455746757</v>
       </c>
       <c r="E48">
-        <v>5.625999999999999</v>
+        <v>6.007</v>
       </c>
       <c r="F48">
-        <v>17.526</v>
+        <v>17.907</v>
       </c>
       <c r="G48">
         <v>1.22</v>
@@ -5223,45 +5223,45 @@
         <v>5.88</v>
       </c>
       <c r="M48">
-        <v>0.9516618</v>
+        <v>0.9902571</v>
       </c>
       <c r="N48">
-        <v>4.9283382</v>
+        <v>4.8897429</v>
       </c>
       <c r="O48">
-        <v>0.73925073</v>
+        <v>0.7334614349999999</v>
       </c>
       <c r="P48">
-        <v>4.18908747</v>
+        <v>4.156281465</v>
       </c>
       <c r="Q48">
-        <v>5.93908747</v>
+        <v>5.906281465</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1236758599701845</v>
+        <v>0.1250173771250931</v>
       </c>
       <c r="T48">
-        <v>1.014983518770735</v>
+        <v>1.032467984469114</v>
       </c>
       <c r="U48">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V48">
         <v>0.15</v>
       </c>
       <c r="W48">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>6.178665572160194</v>
+        <v>5.937851897249714</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08835155987629933</v>
+        <v>0.08829585536869906</v>
       </c>
       <c r="C49">
-        <v>23.63256455746756</v>
+        <v>23.27736353665149</v>
       </c>
       <c r="D49">
-        <v>40.31956455746757</v>
+        <v>40.34536353665149</v>
       </c>
       <c r="E49">
-        <v>6.007</v>
+        <v>6.388000000000003</v>
       </c>
       <c r="F49">
-        <v>17.907</v>
+        <v>18.288</v>
       </c>
       <c r="G49">
         <v>1.22</v>
@@ -5305,28 +5305,28 @@
         <v>5.88</v>
       </c>
       <c r="M49">
-        <v>0.9902571</v>
+        <v>1.0113264</v>
       </c>
       <c r="N49">
-        <v>4.8897429</v>
+        <v>4.868673599999999</v>
       </c>
       <c r="O49">
-        <v>0.7334614349999999</v>
+        <v>0.7303010399999998</v>
       </c>
       <c r="P49">
-        <v>4.156281465</v>
+        <v>4.13837256</v>
       </c>
       <c r="Q49">
-        <v>5.906281465</v>
+        <v>5.88837256</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1250173771250931</v>
+        <v>0.126410491093652</v>
       </c>
       <c r="T49">
-        <v>1.032467984469114</v>
+        <v>1.050624929617431</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.937851897249714</v>
+        <v>5.814146649390343</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08829585536869906</v>
+        <v>0.08824015086109879</v>
       </c>
       <c r="C50">
-        <v>23.27736353665149</v>
+        <v>22.92219555257534</v>
       </c>
       <c r="D50">
-        <v>40.34536353665149</v>
+        <v>40.37119555257534</v>
       </c>
       <c r="E50">
-        <v>6.388</v>
+        <v>6.769</v>
       </c>
       <c r="F50">
-        <v>18.288</v>
+        <v>18.669</v>
       </c>
       <c r="G50">
         <v>1.22</v>
@@ -5387,28 +5387,28 @@
         <v>5.88</v>
       </c>
       <c r="M50">
-        <v>1.0113264</v>
+        <v>1.0323957</v>
       </c>
       <c r="N50">
-        <v>4.8686736</v>
+        <v>4.8476043</v>
       </c>
       <c r="O50">
-        <v>0.73030104</v>
+        <v>0.7271406449999999</v>
       </c>
       <c r="P50">
-        <v>4.138372560000001</v>
+        <v>4.120463655</v>
       </c>
       <c r="Q50">
-        <v>5.888372560000001</v>
+        <v>5.870463655</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.126410491093652</v>
+        <v>0.1278582369825467</v>
       </c>
       <c r="T50">
-        <v>1.050624929617431</v>
+        <v>1.069493911830388</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.814146649390346</v>
+        <v>5.695490595321154</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08824015086109879</v>
+        <v>0.08818444635349854</v>
       </c>
       <c r="C51">
-        <v>22.92219555257534</v>
+        <v>22.56706066873727</v>
       </c>
       <c r="D51">
-        <v>40.37119555257534</v>
+        <v>40.39706066873728</v>
       </c>
       <c r="E51">
-        <v>6.769</v>
+        <v>7.15</v>
       </c>
       <c r="F51">
-        <v>18.669</v>
+        <v>19.05</v>
       </c>
       <c r="G51">
         <v>1.22</v>
@@ -5469,28 +5469,28 @@
         <v>5.88</v>
       </c>
       <c r="M51">
-        <v>1.0323957</v>
+        <v>1.053465</v>
       </c>
       <c r="N51">
-        <v>4.8476043</v>
+        <v>4.826535</v>
       </c>
       <c r="O51">
-        <v>0.7271406449999999</v>
+        <v>0.72398025</v>
       </c>
       <c r="P51">
-        <v>4.120463655</v>
+        <v>4.102554749999999</v>
       </c>
       <c r="Q51">
-        <v>5.870463655</v>
+        <v>5.852554749999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1278582369825467</v>
+        <v>0.1293638927069971</v>
       </c>
       <c r="T51">
-        <v>1.069493911830388</v>
+        <v>1.089117653331863</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.695490595321154</v>
+        <v>5.581580783414731</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08818444635349854</v>
+        <v>0.08812874184589828</v>
       </c>
       <c r="C52">
-        <v>22.56706066873727</v>
+        <v>22.21195894879832</v>
       </c>
       <c r="D52">
-        <v>40.39706066873728</v>
+        <v>40.42295894879832</v>
       </c>
       <c r="E52">
-        <v>7.15</v>
+        <v>7.531000000000001</v>
       </c>
       <c r="F52">
-        <v>19.05</v>
+        <v>19.431</v>
       </c>
       <c r="G52">
         <v>1.22</v>
@@ -5551,28 +5551,28 @@
         <v>5.88</v>
       </c>
       <c r="M52">
-        <v>1.053465</v>
+        <v>1.0745343</v>
       </c>
       <c r="N52">
-        <v>4.826535</v>
+        <v>4.8054657</v>
       </c>
       <c r="O52">
-        <v>0.72398025</v>
+        <v>0.720819855</v>
       </c>
       <c r="P52">
-        <v>4.102554749999999</v>
+        <v>4.084645845</v>
       </c>
       <c r="Q52">
-        <v>5.852554749999999</v>
+        <v>5.834645845</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1293638927069971</v>
+        <v>0.1309310037671393</v>
       </c>
       <c r="T52">
-        <v>1.089117653331863</v>
+        <v>1.109542363874215</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.581580783414731</v>
+        <v>5.472138022955619</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08812874184589828</v>
+        <v>0.08807303733829799</v>
       </c>
       <c r="C53">
-        <v>22.21195894879832</v>
+        <v>21.85689045658286</v>
       </c>
       <c r="D53">
-        <v>40.42295894879832</v>
+        <v>40.44889045658286</v>
       </c>
       <c r="E53">
-        <v>7.531000000000001</v>
+        <v>7.912000000000001</v>
       </c>
       <c r="F53">
-        <v>19.431</v>
+        <v>19.812</v>
       </c>
       <c r="G53">
         <v>1.22</v>
@@ -5633,28 +5633,28 @@
         <v>5.88</v>
       </c>
       <c r="M53">
-        <v>1.0745343</v>
+        <v>1.0956036</v>
       </c>
       <c r="N53">
-        <v>4.8054657</v>
+        <v>4.7843964</v>
       </c>
       <c r="O53">
-        <v>0.720819855</v>
+        <v>0.71765946</v>
       </c>
       <c r="P53">
-        <v>4.084645845</v>
+        <v>4.06673694</v>
       </c>
       <c r="Q53">
-        <v>5.834645845</v>
+        <v>5.81673694</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1309310037671393</v>
+        <v>0.1325634111214542</v>
       </c>
       <c r="T53">
-        <v>1.109542363874215</v>
+        <v>1.130818104022498</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.472138022955619</v>
+        <v>5.366904599437242</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08807303733829799</v>
+        <v>0.08801733283069774</v>
       </c>
       <c r="C54">
-        <v>21.85689045658286</v>
+        <v>21.5018552560791</v>
       </c>
       <c r="D54">
-        <v>40.44889045658286</v>
+        <v>40.4748552560791</v>
       </c>
       <c r="E54">
-        <v>7.912000000000001</v>
+        <v>8.293000000000001</v>
       </c>
       <c r="F54">
-        <v>19.812</v>
+        <v>20.193</v>
       </c>
       <c r="G54">
         <v>1.22</v>
@@ -5715,28 +5715,28 @@
         <v>5.88</v>
       </c>
       <c r="M54">
-        <v>1.0956036</v>
+        <v>1.1166729</v>
       </c>
       <c r="N54">
-        <v>4.7843964</v>
+        <v>4.7633271</v>
       </c>
       <c r="O54">
-        <v>0.71765946</v>
+        <v>0.7144990649999999</v>
       </c>
       <c r="P54">
-        <v>4.06673694</v>
+        <v>4.048828035</v>
       </c>
       <c r="Q54">
-        <v>5.81673694</v>
+        <v>5.798828035</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1325634111214542</v>
+        <v>0.1342652826185058</v>
       </c>
       <c r="T54">
-        <v>1.130818104022498</v>
+        <v>1.152999194815388</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.366904599437242</v>
+        <v>5.265642248504463</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08801733283069774</v>
+        <v>0.08796162832309745</v>
       </c>
       <c r="C55">
-        <v>21.5018552560791</v>
+        <v>21.14685341143973</v>
       </c>
       <c r="D55">
-        <v>40.4748552560791</v>
+        <v>40.50085341143973</v>
       </c>
       <c r="E55">
-        <v>8.293000000000001</v>
+        <v>8.674000000000001</v>
       </c>
       <c r="F55">
-        <v>20.193</v>
+        <v>20.574</v>
       </c>
       <c r="G55">
         <v>1.22</v>
@@ -5797,28 +5797,28 @@
         <v>5.88</v>
       </c>
       <c r="M55">
-        <v>1.1166729</v>
+        <v>1.1377422</v>
       </c>
       <c r="N55">
-        <v>4.7633271</v>
+        <v>4.7422578</v>
       </c>
       <c r="O55">
-        <v>0.7144990649999999</v>
+        <v>0.71133867</v>
       </c>
       <c r="P55">
-        <v>4.048828035</v>
+        <v>4.03091913</v>
       </c>
       <c r="Q55">
-        <v>5.798828035</v>
+        <v>5.78091913</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1342652826185058</v>
+        <v>0.1360411485284727</v>
       </c>
       <c r="T55">
-        <v>1.152999194815388</v>
+        <v>1.176144680860144</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.265642248504463</v>
+        <v>5.168130355013639</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08796162832309745</v>
+        <v>0.08790592381549719</v>
       </c>
       <c r="C56">
-        <v>21.14685341143973</v>
+        <v>20.79188498698231</v>
       </c>
       <c r="D56">
-        <v>40.50085341143973</v>
+        <v>40.52688498698231</v>
       </c>
       <c r="E56">
-        <v>8.674000000000001</v>
+        <v>9.055000000000001</v>
       </c>
       <c r="F56">
-        <v>20.574</v>
+        <v>20.955</v>
       </c>
       <c r="G56">
         <v>1.22</v>
@@ -5879,28 +5879,28 @@
         <v>5.88</v>
       </c>
       <c r="M56">
-        <v>1.1377422</v>
+        <v>1.1588115</v>
       </c>
       <c r="N56">
-        <v>4.7422578</v>
+        <v>4.7211885</v>
       </c>
       <c r="O56">
-        <v>0.71133867</v>
+        <v>0.708178275</v>
       </c>
       <c r="P56">
-        <v>4.03091913</v>
+        <v>4.013010225</v>
       </c>
       <c r="Q56">
-        <v>5.78091913</v>
+        <v>5.763010225</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1360411485284727</v>
+        <v>0.137895941812216</v>
       </c>
       <c r="T56">
-        <v>1.176144680860144</v>
+        <v>1.200318855173555</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.168130355013639</v>
+        <v>5.074164348558846</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08790592381549719</v>
+        <v>0.08785021930789692</v>
       </c>
       <c r="C57">
-        <v>20.79188498698231</v>
+        <v>20.4369500471899</v>
       </c>
       <c r="D57">
-        <v>40.52688498698231</v>
+        <v>40.5529500471899</v>
       </c>
       <c r="E57">
-        <v>9.055000000000001</v>
+        <v>9.436000000000002</v>
       </c>
       <c r="F57">
-        <v>20.955</v>
+        <v>21.336</v>
       </c>
       <c r="G57">
         <v>1.22</v>
@@ -5961,28 +5961,28 @@
         <v>5.88</v>
       </c>
       <c r="M57">
-        <v>1.1588115</v>
+        <v>1.1798808</v>
       </c>
       <c r="N57">
-        <v>4.7211885</v>
+        <v>4.7001192</v>
       </c>
       <c r="O57">
-        <v>0.708178275</v>
+        <v>0.7050178799999999</v>
       </c>
       <c r="P57">
-        <v>4.013010225</v>
+        <v>3.99510132</v>
       </c>
       <c r="Q57">
-        <v>5.763010225</v>
+        <v>5.74510132</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.137895941812216</v>
+        <v>0.1398350438815839</v>
       </c>
       <c r="T57">
-        <v>1.200318855173555</v>
+        <v>1.225591855592121</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.074164348558846</v>
+        <v>4.983554270906009</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08785021930789692</v>
+        <v>0.08779451480029667</v>
       </c>
       <c r="C58">
-        <v>20.4369500471899</v>
+        <v>20.08204865671154</v>
       </c>
       <c r="D58">
-        <v>40.5529500471899</v>
+        <v>40.57904865671154</v>
       </c>
       <c r="E58">
-        <v>9.436000000000002</v>
+        <v>9.817000000000002</v>
       </c>
       <c r="F58">
-        <v>21.336</v>
+        <v>21.717</v>
       </c>
       <c r="G58">
         <v>1.22</v>
@@ -6043,28 +6043,28 @@
         <v>5.88</v>
       </c>
       <c r="M58">
-        <v>1.1798808</v>
+        <v>1.2009501</v>
       </c>
       <c r="N58">
-        <v>4.7001192</v>
+        <v>4.6790499</v>
       </c>
       <c r="O58">
-        <v>0.7050178799999999</v>
+        <v>0.701857485</v>
       </c>
       <c r="P58">
-        <v>3.99510132</v>
+        <v>3.977192415</v>
       </c>
       <c r="Q58">
-        <v>5.74510132</v>
+        <v>5.727192414999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1398350438815839</v>
+        <v>0.141864336744876</v>
       </c>
       <c r="T58">
-        <v>1.225591855592121</v>
+        <v>1.252040344402249</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.983554270906009</v>
+        <v>4.896123494223447</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08779451480029667</v>
+        <v>0.0877388102926964</v>
       </c>
       <c r="C59">
-        <v>20.08204865671154</v>
+        <v>19.72718088036282</v>
       </c>
       <c r="D59">
-        <v>40.57904865671154</v>
+        <v>40.60518088036282</v>
       </c>
       <c r="E59">
-        <v>9.817000000000002</v>
+        <v>10.198</v>
       </c>
       <c r="F59">
-        <v>21.717</v>
+        <v>22.098</v>
       </c>
       <c r="G59">
         <v>1.22</v>
@@ -6125,28 +6125,28 @@
         <v>5.88</v>
       </c>
       <c r="M59">
-        <v>1.2009501</v>
+        <v>1.2220194</v>
       </c>
       <c r="N59">
-        <v>4.6790499</v>
+        <v>4.6579806</v>
       </c>
       <c r="O59">
-        <v>0.701857485</v>
+        <v>0.69869709</v>
       </c>
       <c r="P59">
-        <v>3.977192415</v>
+        <v>3.95928351</v>
       </c>
       <c r="Q59">
-        <v>5.727192414999999</v>
+        <v>5.709283510000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.141864336744876</v>
+        <v>0.1439902626016581</v>
       </c>
       <c r="T59">
-        <v>1.252040344402249</v>
+        <v>1.279748285060478</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.896123494223447</v>
+        <v>4.811707571909251</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0877388102926964</v>
+        <v>0.08768310578509611</v>
       </c>
       <c r="C60">
-        <v>19.72718088036282</v>
+        <v>19.3723467831264</v>
       </c>
       <c r="D60">
-        <v>40.60518088036282</v>
+        <v>40.6313467831264</v>
       </c>
       <c r="E60">
-        <v>10.198</v>
+        <v>10.579</v>
       </c>
       <c r="F60">
-        <v>22.098</v>
+        <v>22.479</v>
       </c>
       <c r="G60">
         <v>1.22</v>
@@ -6207,28 +6207,28 @@
         <v>5.88</v>
       </c>
       <c r="M60">
-        <v>1.2220194</v>
+        <v>1.2430887</v>
       </c>
       <c r="N60">
-        <v>4.6579806</v>
+        <v>4.6369113</v>
       </c>
       <c r="O60">
-        <v>0.69869709</v>
+        <v>0.6955366949999999</v>
       </c>
       <c r="P60">
-        <v>3.95928351</v>
+        <v>3.941374605</v>
       </c>
       <c r="Q60">
-        <v>5.709283510000001</v>
+        <v>5.691374605</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1439902626016581</v>
+        <v>0.146219892158771</v>
       </c>
       <c r="T60">
-        <v>1.279748285060477</v>
+        <v>1.308807832580083</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.811707571909251</v>
+        <v>4.730153206283671</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08768310578509611</v>
+        <v>0.08762740127749585</v>
       </c>
       <c r="C61">
-        <v>19.3723467831264</v>
+        <v>19.01754643015249</v>
       </c>
       <c r="D61">
-        <v>40.6313467831264</v>
+        <v>40.65754643015249</v>
       </c>
       <c r="E61">
-        <v>10.579</v>
+        <v>10.96</v>
       </c>
       <c r="F61">
-        <v>22.479</v>
+        <v>22.86</v>
       </c>
       <c r="G61">
         <v>1.22</v>
@@ -6289,28 +6289,28 @@
         <v>5.88</v>
       </c>
       <c r="M61">
-        <v>1.2430887</v>
+        <v>1.264158</v>
       </c>
       <c r="N61">
-        <v>4.6369113</v>
+        <v>4.615842</v>
       </c>
       <c r="O61">
-        <v>0.6955366949999999</v>
+        <v>0.6923762999999999</v>
       </c>
       <c r="P61">
-        <v>3.941374605</v>
+        <v>3.9234657</v>
       </c>
       <c r="Q61">
-        <v>5.691374605</v>
+        <v>5.6734657</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.146219892158771</v>
+        <v>0.1485610031937396</v>
       </c>
       <c r="T61">
-        <v>1.308807832580083</v>
+        <v>1.339320357475669</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.730153206283671</v>
+        <v>4.651317319512275</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08762740127749585</v>
+        <v>0.08757169676989558</v>
       </c>
       <c r="C62">
-        <v>19.01754643015249</v>
+        <v>18.66277988675953</v>
       </c>
       <c r="D62">
-        <v>40.65754643015249</v>
+        <v>40.68377988675953</v>
       </c>
       <c r="E62">
-        <v>10.96</v>
+        <v>11.341</v>
       </c>
       <c r="F62">
-        <v>22.86</v>
+        <v>23.241</v>
       </c>
       <c r="G62">
         <v>1.22</v>
@@ -6371,28 +6371,28 @@
         <v>5.88</v>
       </c>
       <c r="M62">
-        <v>1.264158</v>
+        <v>1.2852273</v>
       </c>
       <c r="N62">
-        <v>4.615842</v>
+        <v>4.5947727</v>
       </c>
       <c r="O62">
-        <v>0.6923762999999999</v>
+        <v>0.689215905</v>
       </c>
       <c r="P62">
-        <v>3.9234657</v>
+        <v>3.905556795</v>
       </c>
       <c r="Q62">
-        <v>5.6734657</v>
+        <v>5.655556795</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1485610031937396</v>
+        <v>0.1510221712048605</v>
       </c>
       <c r="T62">
-        <v>1.339320357475669</v>
+        <v>1.371397627237696</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.651317319512275</v>
+        <v>4.575066215913714</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08757169676989558</v>
+        <v>0.08751599226229531</v>
       </c>
       <c r="C63">
-        <v>18.66277988675953</v>
+        <v>18.3080472184346</v>
       </c>
       <c r="D63">
-        <v>40.68377988675953</v>
+        <v>40.7100472184346</v>
       </c>
       <c r="E63">
-        <v>11.341</v>
+        <v>11.722</v>
       </c>
       <c r="F63">
-        <v>23.241</v>
+        <v>23.622</v>
       </c>
       <c r="G63">
         <v>1.22</v>
@@ -6453,28 +6453,28 @@
         <v>5.88</v>
       </c>
       <c r="M63">
-        <v>1.2852273</v>
+        <v>1.3062966</v>
       </c>
       <c r="N63">
-        <v>4.5947727</v>
+        <v>4.573703399999999</v>
       </c>
       <c r="O63">
-        <v>0.689215905</v>
+        <v>0.6860555099999999</v>
       </c>
       <c r="P63">
-        <v>3.905556795</v>
+        <v>3.887647889999999</v>
       </c>
       <c r="Q63">
-        <v>5.655556795</v>
+        <v>5.637647889999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1510221712048605</v>
+        <v>0.1536128743744614</v>
       </c>
       <c r="T63">
-        <v>1.371397627237696</v>
+        <v>1.405163174355619</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.575066215913714</v>
+        <v>4.501274825334461</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08751599226229531</v>
+        <v>0.08879903775469505</v>
       </c>
       <c r="C64">
-        <v>18.3080472184346</v>
+        <v>17.33051067960788</v>
       </c>
       <c r="D64">
-        <v>40.7100472184346</v>
+        <v>40.11351067960788</v>
       </c>
       <c r="E64">
-        <v>11.722</v>
+        <v>12.103</v>
       </c>
       <c r="F64">
-        <v>23.622</v>
+        <v>24.003</v>
       </c>
       <c r="G64">
         <v>1.22</v>
@@ -6535,45 +6535,45 @@
         <v>5.88</v>
       </c>
       <c r="M64">
-        <v>1.3062966</v>
+        <v>1.3873734</v>
       </c>
       <c r="N64">
-        <v>4.573703399999999</v>
+        <v>4.492626599999999</v>
       </c>
       <c r="O64">
-        <v>0.6860555099999999</v>
+        <v>0.6738939899999999</v>
       </c>
       <c r="P64">
-        <v>3.887647889999999</v>
+        <v>3.81873261</v>
       </c>
       <c r="Q64">
-        <v>5.637647889999999</v>
+        <v>5.56873261</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1536128743744614</v>
+        <v>0.1563436155532299</v>
       </c>
       <c r="T64">
-        <v>1.405163174355619</v>
+        <v>1.440753886182618</v>
       </c>
       <c r="U64">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V64">
         <v>0.15</v>
       </c>
       <c r="W64">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.501274825334461</v>
+        <v>4.238224547191116</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08879903775469505</v>
+        <v>0.08876458324709477</v>
       </c>
       <c r="C65">
-        <v>17.33051067960788</v>
+        <v>16.96530136697808</v>
       </c>
       <c r="D65">
-        <v>40.11351067960788</v>
+        <v>40.12930136697808</v>
       </c>
       <c r="E65">
-        <v>12.103</v>
+        <v>12.484</v>
       </c>
       <c r="F65">
-        <v>24.003</v>
+        <v>24.384</v>
       </c>
       <c r="G65">
         <v>1.22</v>
@@ -6617,28 +6617,28 @@
         <v>5.88</v>
       </c>
       <c r="M65">
-        <v>1.3873734</v>
+        <v>1.4093952</v>
       </c>
       <c r="N65">
-        <v>4.492626599999999</v>
+        <v>4.4706048</v>
       </c>
       <c r="O65">
-        <v>0.6738939899999999</v>
+        <v>0.67059072</v>
       </c>
       <c r="P65">
-        <v>3.81873261</v>
+        <v>3.80001408</v>
       </c>
       <c r="Q65">
-        <v>5.56873261</v>
+        <v>5.55001408</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1563436155532299</v>
+        <v>0.1592260645752633</v>
       </c>
       <c r="T65">
-        <v>1.440753886182618</v>
+        <v>1.478321859777784</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.238224547191116</v>
+        <v>4.172002288641256</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08876458324709477</v>
+        <v>0.08873012873949451</v>
       </c>
       <c r="C66">
-        <v>16.96530136697808</v>
+        <v>16.60010449125528</v>
       </c>
       <c r="D66">
-        <v>40.12930136697808</v>
+        <v>40.14510449125528</v>
       </c>
       <c r="E66">
-        <v>12.484</v>
+        <v>12.865</v>
       </c>
       <c r="F66">
-        <v>24.384</v>
+        <v>24.765</v>
       </c>
       <c r="G66">
         <v>1.22</v>
@@ -6699,28 +6699,28 @@
         <v>5.88</v>
       </c>
       <c r="M66">
-        <v>1.4093952</v>
+        <v>1.431417</v>
       </c>
       <c r="N66">
-        <v>4.4706048</v>
+        <v>4.448582999999999</v>
       </c>
       <c r="O66">
-        <v>0.67059072</v>
+        <v>0.6672874499999999</v>
       </c>
       <c r="P66">
-        <v>3.80001408</v>
+        <v>3.781295549999999</v>
       </c>
       <c r="Q66">
-        <v>5.55001408</v>
+        <v>5.531295549999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1592260645752633</v>
+        <v>0.1622732249699843</v>
       </c>
       <c r="T66">
-        <v>1.478321859777784</v>
+        <v>1.518036574721246</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.172002288641256</v>
+        <v>4.107817638046773</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08873012873949451</v>
+        <v>0.08869567423189426</v>
       </c>
       <c r="C67">
-        <v>16.60010449125528</v>
+        <v>16.23492006713845</v>
       </c>
       <c r="D67">
-        <v>40.14510449125528</v>
+        <v>40.16092006713845</v>
       </c>
       <c r="E67">
-        <v>12.865</v>
+        <v>13.246</v>
       </c>
       <c r="F67">
-        <v>24.765</v>
+        <v>25.146</v>
       </c>
       <c r="G67">
         <v>1.22</v>
@@ -6781,28 +6781,28 @@
         <v>5.88</v>
       </c>
       <c r="M67">
-        <v>1.431417</v>
+        <v>1.4534388</v>
       </c>
       <c r="N67">
-        <v>4.448582999999999</v>
+        <v>4.4265612</v>
       </c>
       <c r="O67">
-        <v>0.6672874499999999</v>
+        <v>0.66398418</v>
       </c>
       <c r="P67">
-        <v>3.781295549999999</v>
+        <v>3.76257702</v>
       </c>
       <c r="Q67">
-        <v>5.531295549999999</v>
+        <v>5.51257702</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1622732249699843</v>
+        <v>0.1654996300938066</v>
       </c>
       <c r="T67">
-        <v>1.518036574721246</v>
+        <v>1.560087449367264</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.107817638046773</v>
+        <v>4.045577976864248</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08869567423189426</v>
+        <v>0.09065446972429397</v>
       </c>
       <c r="C68">
-        <v>16.23492006713845</v>
+        <v>14.97412923903753</v>
       </c>
       <c r="D68">
-        <v>40.16092006713845</v>
+        <v>39.28112923903753</v>
       </c>
       <c r="E68">
-        <v>13.246</v>
+        <v>13.627</v>
       </c>
       <c r="F68">
-        <v>25.146</v>
+        <v>25.527</v>
       </c>
       <c r="G68">
         <v>1.22</v>
@@ -6863,45 +6863,45 @@
         <v>5.88</v>
       </c>
       <c r="M68">
-        <v>1.4534388</v>
+        <v>1.5648051</v>
       </c>
       <c r="N68">
-        <v>4.4265612</v>
+        <v>4.3151949</v>
       </c>
       <c r="O68">
-        <v>0.66398418</v>
+        <v>0.647279235</v>
       </c>
       <c r="P68">
-        <v>3.76257702</v>
+        <v>3.667915665</v>
       </c>
       <c r="Q68">
-        <v>5.51257702</v>
+        <v>5.417915665</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1654996300938066</v>
+        <v>0.168921574922103</v>
       </c>
       <c r="T68">
-        <v>1.560087449367264</v>
+        <v>1.604686861870616</v>
       </c>
       <c r="U68">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V68">
         <v>0.15</v>
       </c>
       <c r="W68">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>4.045577976864248</v>
+        <v>3.75765646469327</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09065446972429397</v>
+        <v>0.09064976521669371</v>
       </c>
       <c r="C69">
-        <v>14.97412923903753</v>
+        <v>14.59519608290068</v>
       </c>
       <c r="D69">
-        <v>39.28112923903753</v>
+        <v>39.28319608290068</v>
       </c>
       <c r="E69">
-        <v>13.627</v>
+        <v>14.008</v>
       </c>
       <c r="F69">
-        <v>25.527</v>
+        <v>25.908</v>
       </c>
       <c r="G69">
         <v>1.22</v>
@@ -6945,28 +6945,28 @@
         <v>5.88</v>
       </c>
       <c r="M69">
-        <v>1.5648051</v>
+        <v>1.5881604</v>
       </c>
       <c r="N69">
-        <v>4.3151949</v>
+        <v>4.291839599999999</v>
       </c>
       <c r="O69">
-        <v>0.647279235</v>
+        <v>0.6437759399999999</v>
       </c>
       <c r="P69">
-        <v>3.667915665</v>
+        <v>3.64806366</v>
       </c>
       <c r="Q69">
-        <v>5.417915665</v>
+        <v>5.39806366</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.168921574922103</v>
+        <v>0.1725573913021679</v>
       </c>
       <c r="T69">
-        <v>1.604686861870616</v>
+        <v>1.652073737655428</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.75765646469327</v>
+        <v>3.702396810800722</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09064976521669371</v>
+        <v>0.09064506070909345</v>
       </c>
       <c r="C70">
-        <v>14.59519608290068</v>
+        <v>14.21626314427633</v>
       </c>
       <c r="D70">
-        <v>39.28319608290068</v>
+        <v>39.28526314427633</v>
       </c>
       <c r="E70">
-        <v>14.008</v>
+        <v>14.389</v>
       </c>
       <c r="F70">
-        <v>25.908</v>
+        <v>26.289</v>
       </c>
       <c r="G70">
         <v>1.22</v>
@@ -7027,28 +7027,28 @@
         <v>5.88</v>
       </c>
       <c r="M70">
-        <v>1.5881604</v>
+        <v>1.6115157</v>
       </c>
       <c r="N70">
-        <v>4.291839599999999</v>
+        <v>4.2684843</v>
       </c>
       <c r="O70">
-        <v>0.6437759399999999</v>
+        <v>0.6402726449999999</v>
       </c>
       <c r="P70">
-        <v>3.64806366</v>
+        <v>3.628211655</v>
       </c>
       <c r="Q70">
-        <v>5.39806366</v>
+        <v>5.378211654999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1725573913021679</v>
+        <v>0.1764277764809466</v>
       </c>
       <c r="T70">
-        <v>1.652073737655428</v>
+        <v>1.702517831232808</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.702396810800722</v>
+        <v>3.648738886006509</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09064506070909345</v>
+        <v>0.09064035620149317</v>
       </c>
       <c r="C71">
-        <v>14.21626314427633</v>
+        <v>13.83733042319882</v>
       </c>
       <c r="D71">
-        <v>39.28526314427633</v>
+        <v>39.28733042319882</v>
       </c>
       <c r="E71">
-        <v>14.389</v>
+        <v>14.77</v>
       </c>
       <c r="F71">
-        <v>26.289</v>
+        <v>26.67000000000001</v>
       </c>
       <c r="G71">
         <v>1.22</v>
@@ -7109,28 +7109,28 @@
         <v>5.88</v>
       </c>
       <c r="M71">
-        <v>1.6115157</v>
+        <v>1.634871</v>
       </c>
       <c r="N71">
-        <v>4.2684843</v>
+        <v>4.245128999999999</v>
       </c>
       <c r="O71">
-        <v>0.6402726449999999</v>
+        <v>0.6367693499999999</v>
       </c>
       <c r="P71">
-        <v>3.628211655</v>
+        <v>3.60835965</v>
       </c>
       <c r="Q71">
-        <v>5.378211654999999</v>
+        <v>5.35835965</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1764277764809466</v>
+        <v>0.1805561873383106</v>
       </c>
       <c r="T71">
-        <v>1.702517831232808</v>
+        <v>1.756324864382014</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.648738886006509</v>
+        <v>3.596614044777844</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09064035620149317</v>
+        <v>0.09063565169389291</v>
       </c>
       <c r="C72">
-        <v>13.83733042319882</v>
+        <v>13.4583979197025</v>
       </c>
       <c r="D72">
-        <v>39.28733042319882</v>
+        <v>39.2893979197025</v>
       </c>
       <c r="E72">
-        <v>14.77</v>
+        <v>15.15100000000001</v>
       </c>
       <c r="F72">
-        <v>26.67000000000001</v>
+        <v>27.05100000000001</v>
       </c>
       <c r="G72">
         <v>1.22</v>
@@ -7191,28 +7191,28 @@
         <v>5.88</v>
       </c>
       <c r="M72">
-        <v>1.634871</v>
+        <v>1.6582263</v>
       </c>
       <c r="N72">
-        <v>4.245128999999999</v>
+        <v>4.2217737</v>
       </c>
       <c r="O72">
-        <v>0.6367693499999999</v>
+        <v>0.633266055</v>
       </c>
       <c r="P72">
-        <v>3.60835965</v>
+        <v>3.588507645</v>
       </c>
       <c r="Q72">
-        <v>5.35835965</v>
+        <v>5.338507645</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1805561873383106</v>
+        <v>0.1849693161858377</v>
       </c>
       <c r="T72">
-        <v>1.756324864382014</v>
+        <v>1.813842727403579</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.596614044777844</v>
+        <v>3.545957508935903</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09063565169389291</v>
+        <v>0.09234454718629265</v>
       </c>
       <c r="C73">
-        <v>13.4583979197025</v>
+        <v>12.34043538164216</v>
       </c>
       <c r="D73">
-        <v>39.2893979197025</v>
+        <v>38.55243538164216</v>
       </c>
       <c r="E73">
-        <v>15.151</v>
+        <v>15.532</v>
       </c>
       <c r="F73">
-        <v>27.051</v>
+        <v>27.432</v>
       </c>
       <c r="G73">
         <v>1.22</v>
@@ -7273,45 +7273,45 @@
         <v>5.88</v>
       </c>
       <c r="M73">
-        <v>1.6582263</v>
+        <v>1.7583912</v>
       </c>
       <c r="N73">
-        <v>4.2217737</v>
+        <v>4.1216088</v>
       </c>
       <c r="O73">
-        <v>0.633266055</v>
+        <v>0.61824132</v>
       </c>
       <c r="P73">
-        <v>3.588507645</v>
+        <v>3.50336748</v>
       </c>
       <c r="Q73">
-        <v>5.338507645</v>
+        <v>5.25336748</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1849693161858376</v>
+        <v>0.1896976685224737</v>
       </c>
       <c r="T73">
-        <v>1.813842727403578</v>
+        <v>1.875469009212397</v>
       </c>
       <c r="U73">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V73">
         <v>0.15</v>
       </c>
       <c r="W73">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.545957508935904</v>
+        <v>3.34396577962856</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09234454718629265</v>
+        <v>0.09236364267869238</v>
       </c>
       <c r="C74">
-        <v>12.34043538164216</v>
+        <v>11.95135659392853</v>
       </c>
       <c r="D74">
-        <v>38.55243538164216</v>
+        <v>38.54435659392853</v>
       </c>
       <c r="E74">
-        <v>15.532</v>
+        <v>15.913</v>
       </c>
       <c r="F74">
-        <v>27.432</v>
+        <v>27.813</v>
       </c>
       <c r="G74">
         <v>1.22</v>
@@ -7355,28 +7355,28 @@
         <v>5.88</v>
       </c>
       <c r="M74">
-        <v>1.7583912</v>
+        <v>1.7828133</v>
       </c>
       <c r="N74">
-        <v>4.1216088</v>
+        <v>4.0971867</v>
       </c>
       <c r="O74">
-        <v>0.61824132</v>
+        <v>0.6145780049999999</v>
       </c>
       <c r="P74">
-        <v>3.50336748</v>
+        <v>3.482608695</v>
       </c>
       <c r="Q74">
-        <v>5.25336748</v>
+        <v>5.232608695</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1896976685224737</v>
+        <v>0.1947762691803421</v>
       </c>
       <c r="T74">
-        <v>1.875469009212397</v>
+        <v>1.941660200784833</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.34396577962856</v>
+        <v>3.29815802922269</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09236364267869238</v>
+        <v>0.0923827381710921</v>
       </c>
       <c r="C75">
-        <v>11.95135659392853</v>
+        <v>11.56228119137779</v>
       </c>
       <c r="D75">
-        <v>38.54435659392853</v>
+        <v>38.53628119137779</v>
       </c>
       <c r="E75">
-        <v>15.913</v>
+        <v>16.294</v>
       </c>
       <c r="F75">
-        <v>27.813</v>
+        <v>28.194</v>
       </c>
       <c r="G75">
         <v>1.22</v>
@@ -7437,28 +7437,28 @@
         <v>5.88</v>
       </c>
       <c r="M75">
-        <v>1.7828133</v>
+        <v>1.8072354</v>
       </c>
       <c r="N75">
-        <v>4.0971867</v>
+        <v>4.072764599999999</v>
       </c>
       <c r="O75">
-        <v>0.6145780049999999</v>
+        <v>0.6109146899999999</v>
       </c>
       <c r="P75">
-        <v>3.482608695</v>
+        <v>3.461849909999999</v>
       </c>
       <c r="Q75">
-        <v>5.232608695</v>
+        <v>5.21184991</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1947762691803421</v>
+        <v>0.2002455314272773</v>
       </c>
       <c r="T75">
-        <v>1.941660200784833</v>
+        <v>2.012943022478225</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.29815802922269</v>
+        <v>3.253588326125085</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0923827381710921</v>
+        <v>0.09240183366349183</v>
       </c>
       <c r="C76">
-        <v>11.56228119137779</v>
+        <v>11.17320917186273</v>
       </c>
       <c r="D76">
-        <v>38.53628119137779</v>
+        <v>38.52820917186273</v>
       </c>
       <c r="E76">
-        <v>16.294</v>
+        <v>16.675</v>
       </c>
       <c r="F76">
-        <v>28.194</v>
+        <v>28.575</v>
       </c>
       <c r="G76">
         <v>1.22</v>
@@ -7519,28 +7519,28 @@
         <v>5.88</v>
       </c>
       <c r="M76">
-        <v>1.8072354</v>
+        <v>1.8316575</v>
       </c>
       <c r="N76">
-        <v>4.072764599999999</v>
+        <v>4.0483425</v>
       </c>
       <c r="O76">
-        <v>0.6109146899999999</v>
+        <v>0.6072513749999999</v>
       </c>
       <c r="P76">
-        <v>3.461849909999999</v>
+        <v>3.441091125</v>
       </c>
       <c r="Q76">
-        <v>5.21184991</v>
+        <v>5.191091125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2002455314272773</v>
+        <v>0.2061523346539674</v>
       </c>
       <c r="T76">
-        <v>2.012943022478225</v>
+        <v>2.089928469907089</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.253588326125085</v>
+        <v>3.210207148443417</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09240183366349183</v>
+        <v>0.09242092915589156</v>
       </c>
       <c r="C77">
-        <v>11.17320917186273</v>
+        <v>10.7841405332579</v>
       </c>
       <c r="D77">
-        <v>38.52820917186273</v>
+        <v>38.5201405332579</v>
       </c>
       <c r="E77">
-        <v>16.675</v>
+        <v>17.056</v>
       </c>
       <c r="F77">
-        <v>28.575</v>
+        <v>28.956</v>
       </c>
       <c r="G77">
         <v>1.22</v>
@@ -7601,28 +7601,28 @@
         <v>5.88</v>
       </c>
       <c r="M77">
-        <v>1.8316575</v>
+        <v>1.8560796</v>
       </c>
       <c r="N77">
-        <v>4.0483425</v>
+        <v>4.0239204</v>
       </c>
       <c r="O77">
-        <v>0.6072513749999999</v>
+        <v>0.60358806</v>
       </c>
       <c r="P77">
-        <v>3.441091125</v>
+        <v>3.42033234</v>
       </c>
       <c r="Q77">
-        <v>5.191091125</v>
+        <v>5.17033234</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2061523346539674</v>
+        <v>0.2125513714828816</v>
       </c>
       <c r="T77">
-        <v>2.089928469907089</v>
+        <v>2.173329371288358</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.210207148443417</v>
+        <v>3.167967580700741</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09242092915589156</v>
+        <v>0.09244002464829131</v>
       </c>
       <c r="C78">
-        <v>10.7841405332579</v>
+        <v>10.39507527343962</v>
       </c>
       <c r="D78">
-        <v>38.5201405332579</v>
+        <v>38.51207527343963</v>
       </c>
       <c r="E78">
-        <v>17.056</v>
+        <v>17.437</v>
       </c>
       <c r="F78">
-        <v>28.956</v>
+        <v>29.337</v>
       </c>
       <c r="G78">
         <v>1.22</v>
@@ -7683,28 +7683,28 @@
         <v>5.88</v>
       </c>
       <c r="M78">
-        <v>1.8560796</v>
+        <v>1.8805017</v>
       </c>
       <c r="N78">
-        <v>4.0239204</v>
+        <v>3.9994983</v>
       </c>
       <c r="O78">
-        <v>0.60358806</v>
+        <v>0.5999247449999999</v>
       </c>
       <c r="P78">
-        <v>3.42033234</v>
+        <v>3.399573554999999</v>
       </c>
       <c r="Q78">
-        <v>5.17033234</v>
+        <v>5.149573555</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2125513714828816</v>
+        <v>0.2195068462969187</v>
       </c>
       <c r="T78">
-        <v>2.173329371288358</v>
+        <v>2.26398252496365</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.167967580700741</v>
+        <v>3.126825144587744</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09244002464829131</v>
+        <v>0.09245912014069103</v>
       </c>
       <c r="C79">
-        <v>10.39507527343962</v>
+        <v>10.00601339028604</v>
       </c>
       <c r="D79">
-        <v>38.51207527343963</v>
+        <v>38.50401339028605</v>
       </c>
       <c r="E79">
-        <v>17.437</v>
+        <v>17.818</v>
       </c>
       <c r="F79">
-        <v>29.337</v>
+        <v>29.718</v>
       </c>
       <c r="G79">
         <v>1.22</v>
@@ -7765,28 +7765,28 @@
         <v>5.88</v>
       </c>
       <c r="M79">
-        <v>1.8805017</v>
+        <v>1.9049238</v>
       </c>
       <c r="N79">
-        <v>3.9994983</v>
+        <v>3.975076199999999</v>
       </c>
       <c r="O79">
-        <v>0.5999247449999999</v>
+        <v>0.5962614299999999</v>
       </c>
       <c r="P79">
-        <v>3.399573554999999</v>
+        <v>3.37881477</v>
       </c>
       <c r="Q79">
-        <v>5.149573555</v>
+        <v>5.12881477</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2195068462969187</v>
+        <v>0.2270946370031411</v>
       </c>
       <c r="T79">
-        <v>2.26398252496365</v>
+        <v>2.362876874427605</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.126825144587744</v>
+        <v>3.086737642734055</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09245912014069103</v>
+        <v>0.09247821563309076</v>
       </c>
       <c r="C80">
-        <v>10.00601339028604</v>
+        <v>9.616954881677053</v>
       </c>
       <c r="D80">
-        <v>38.50401339028605</v>
+        <v>38.49595488167706</v>
       </c>
       <c r="E80">
-        <v>17.818</v>
+        <v>18.19900000000001</v>
       </c>
       <c r="F80">
-        <v>29.718</v>
+        <v>30.099</v>
       </c>
       <c r="G80">
         <v>1.22</v>
@@ -7847,28 +7847,28 @@
         <v>5.88</v>
       </c>
       <c r="M80">
-        <v>1.9049238</v>
+        <v>1.9293459</v>
       </c>
       <c r="N80">
-        <v>3.975076199999999</v>
+        <v>3.9506541</v>
       </c>
       <c r="O80">
-        <v>0.5962614299999999</v>
+        <v>0.5925981149999999</v>
       </c>
       <c r="P80">
-        <v>3.37881477</v>
+        <v>3.358055985</v>
       </c>
       <c r="Q80">
-        <v>5.12881477</v>
+        <v>5.108055985</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2270946370031411</v>
+        <v>0.2354050744432894</v>
       </c>
       <c r="T80">
-        <v>2.362876874427605</v>
+        <v>2.471189733364318</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.086737642734055</v>
+        <v>3.047665014345017</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09247821563309076</v>
+        <v>0.09249731112549049</v>
       </c>
       <c r="C81">
-        <v>9.616954881677053</v>
+        <v>9.227899745494291</v>
       </c>
       <c r="D81">
-        <v>38.49595488167706</v>
+        <v>38.4878997454943</v>
       </c>
       <c r="E81">
-        <v>18.19900000000001</v>
+        <v>18.58000000000001</v>
       </c>
       <c r="F81">
-        <v>30.099</v>
+        <v>30.48</v>
       </c>
       <c r="G81">
         <v>1.22</v>
@@ -7929,28 +7929,28 @@
         <v>5.88</v>
       </c>
       <c r="M81">
-        <v>1.9293459</v>
+        <v>1.953768</v>
       </c>
       <c r="N81">
-        <v>3.9506541</v>
+        <v>3.926232</v>
       </c>
       <c r="O81">
-        <v>0.5925981149999999</v>
+        <v>0.5889348</v>
       </c>
       <c r="P81">
-        <v>3.358055985</v>
+        <v>3.3372972</v>
       </c>
       <c r="Q81">
-        <v>5.108055985</v>
+        <v>5.0872972</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2354050744432894</v>
+        <v>0.2445465556274525</v>
       </c>
       <c r="T81">
-        <v>2.471189733364318</v>
+        <v>2.590333878194702</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.047665014345017</v>
+        <v>3.009569201665704</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09249731112549049</v>
+        <v>0.09788670661789023</v>
       </c>
       <c r="C82">
-        <v>9.227899745494291</v>
+        <v>6.700690277564533</v>
       </c>
       <c r="D82">
-        <v>38.4878997454943</v>
+        <v>36.34169027756454</v>
       </c>
       <c r="E82">
-        <v>18.58000000000001</v>
+        <v>18.96100000000001</v>
       </c>
       <c r="F82">
-        <v>30.48</v>
+        <v>30.861</v>
       </c>
       <c r="G82">
         <v>1.22</v>
@@ -8011,45 +8011,45 @@
         <v>5.88</v>
       </c>
       <c r="M82">
-        <v>1.953768</v>
+        <v>2.218905900000001</v>
       </c>
       <c r="N82">
-        <v>3.926232</v>
+        <v>3.661094099999999</v>
       </c>
       <c r="O82">
-        <v>0.5889348</v>
+        <v>0.5491641149999998</v>
       </c>
       <c r="P82">
-        <v>3.3372972</v>
+        <v>3.111929984999999</v>
       </c>
       <c r="Q82">
-        <v>5.0872972</v>
+        <v>4.861929985</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2445465556274525</v>
+        <v>0.254650297988896</v>
       </c>
       <c r="T82">
-        <v>2.590333878194702</v>
+        <v>2.7220195119546</v>
       </c>
       <c r="U82">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V82">
         <v>0.15</v>
       </c>
       <c r="W82">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y82">
-        <v>3.009569201665704</v>
+        <v>2.64995464656703</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09788670661789023</v>
+        <v>0.09797210211028996</v>
       </c>
       <c r="C83">
-        <v>6.700690277564533</v>
+        <v>6.287608062406036</v>
       </c>
       <c r="D83">
-        <v>36.34169027756454</v>
+        <v>36.30960806240604</v>
       </c>
       <c r="E83">
-        <v>18.96100000000001</v>
+        <v>19.34200000000001</v>
       </c>
       <c r="F83">
-        <v>30.861</v>
+        <v>31.242</v>
       </c>
       <c r="G83">
         <v>1.22</v>
@@ -8093,28 +8093,28 @@
         <v>5.88</v>
       </c>
       <c r="M83">
-        <v>2.218905900000001</v>
+        <v>2.246299800000001</v>
       </c>
       <c r="N83">
-        <v>3.661094099999999</v>
+        <v>3.633700199999999</v>
       </c>
       <c r="O83">
-        <v>0.5491641149999998</v>
+        <v>0.5450550299999999</v>
       </c>
       <c r="P83">
-        <v>3.111929984999999</v>
+        <v>3.088645169999999</v>
       </c>
       <c r="Q83">
-        <v>4.861929985</v>
+        <v>4.838645169999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.254650297988896</v>
+        <v>0.2658766783904998</v>
       </c>
       <c r="T83">
-        <v>2.7220195119546</v>
+        <v>2.868336882798932</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.64995464656703</v>
+        <v>2.617638126486945</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09797210211028996</v>
+        <v>0.0980574976026897</v>
       </c>
       <c r="C84">
-        <v>6.287608062406036</v>
+        <v>5.874582441241444</v>
       </c>
       <c r="D84">
-        <v>36.30960806240604</v>
+        <v>36.27758244124145</v>
       </c>
       <c r="E84">
-        <v>19.34200000000001</v>
+        <v>19.72300000000001</v>
       </c>
       <c r="F84">
-        <v>31.242</v>
+        <v>31.623</v>
       </c>
       <c r="G84">
         <v>1.22</v>
@@ -8175,28 +8175,28 @@
         <v>5.88</v>
       </c>
       <c r="M84">
-        <v>2.246299800000001</v>
+        <v>2.2736937</v>
       </c>
       <c r="N84">
-        <v>3.633700199999999</v>
+        <v>3.6063063</v>
       </c>
       <c r="O84">
-        <v>0.5450550299999999</v>
+        <v>0.5409459449999999</v>
       </c>
       <c r="P84">
-        <v>3.088645169999999</v>
+        <v>3.065360355</v>
       </c>
       <c r="Q84">
-        <v>4.838645169999999</v>
+        <v>4.815360354999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2658766783904998</v>
+        <v>0.2784238094275865</v>
       </c>
       <c r="T84">
-        <v>2.868336882798932</v>
+        <v>3.031868061977891</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.617638126486945</v>
+        <v>2.58610031773409</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0980574976026897</v>
+        <v>0.09814289309508943</v>
       </c>
       <c r="C85">
-        <v>5.874582441241444</v>
+        <v>5.461613264452467</v>
       </c>
       <c r="D85">
-        <v>36.27758244124145</v>
+        <v>36.24561326445247</v>
       </c>
       <c r="E85">
-        <v>19.72300000000001</v>
+        <v>20.10400000000001</v>
       </c>
       <c r="F85">
-        <v>31.623</v>
+        <v>32.004</v>
       </c>
       <c r="G85">
         <v>1.22</v>
@@ -8257,28 +8257,28 @@
         <v>5.88</v>
       </c>
       <c r="M85">
-        <v>2.2736937</v>
+        <v>2.301087600000001</v>
       </c>
       <c r="N85">
-        <v>3.6063063</v>
+        <v>3.578912399999999</v>
       </c>
       <c r="O85">
-        <v>0.5409459449999999</v>
+        <v>0.5368368599999999</v>
       </c>
       <c r="P85">
-        <v>3.065360355</v>
+        <v>3.042075539999999</v>
       </c>
       <c r="Q85">
-        <v>4.815360354999999</v>
+        <v>4.792075539999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2784238094275865</v>
+        <v>0.292539331844309</v>
       </c>
       <c r="T85">
-        <v>3.031868061977891</v>
+        <v>3.215840638554219</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.58610031773409</v>
+        <v>2.555313409189636</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09814289309508943</v>
+        <v>0.09822828858748917</v>
       </c>
       <c r="C86">
-        <v>5.461613264452474</v>
+        <v>5.048700382947736</v>
       </c>
       <c r="D86">
-        <v>36.24561326445247</v>
+        <v>36.21370038294774</v>
       </c>
       <c r="E86">
-        <v>20.104</v>
+        <v>20.485</v>
       </c>
       <c r="F86">
-        <v>32.004</v>
+        <v>32.385</v>
       </c>
       <c r="G86">
         <v>1.22</v>
@@ -8339,28 +8339,28 @@
         <v>5.88</v>
       </c>
       <c r="M86">
-        <v>2.3010876</v>
+        <v>2.3284815</v>
       </c>
       <c r="N86">
-        <v>3.5789124</v>
+        <v>3.5515185</v>
       </c>
       <c r="O86">
-        <v>0.53683686</v>
+        <v>0.5327277749999999</v>
       </c>
       <c r="P86">
-        <v>3.04207554</v>
+        <v>3.018790725</v>
       </c>
       <c r="Q86">
-        <v>4.79207554</v>
+        <v>4.768790725</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2925393318443089</v>
+        <v>0.3085369239165944</v>
       </c>
       <c r="T86">
-        <v>3.215840638554217</v>
+        <v>3.42434289200739</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.555313409189637</v>
+        <v>2.525250898493288</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09822828858748917</v>
+        <v>0.1011645840798889</v>
       </c>
       <c r="C87">
-        <v>5.048700382947736</v>
+        <v>3.603568687454725</v>
       </c>
       <c r="D87">
-        <v>36.21370038294774</v>
+        <v>35.14956868745472</v>
       </c>
       <c r="E87">
-        <v>20.485</v>
+        <v>20.866</v>
       </c>
       <c r="F87">
-        <v>32.385</v>
+        <v>32.766</v>
       </c>
       <c r="G87">
         <v>1.22</v>
@@ -8421,45 +8421,45 @@
         <v>5.88</v>
       </c>
       <c r="M87">
-        <v>2.3284815</v>
+        <v>2.4836628</v>
       </c>
       <c r="N87">
-        <v>3.5515185</v>
+        <v>3.3963372</v>
       </c>
       <c r="O87">
-        <v>0.5327277749999999</v>
+        <v>0.5094505799999999</v>
       </c>
       <c r="P87">
-        <v>3.018790725</v>
+        <v>2.88688662</v>
       </c>
       <c r="Q87">
-        <v>4.768790725</v>
+        <v>4.63688662</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3085369239165944</v>
+        <v>0.3268198862849206</v>
       </c>
       <c r="T87">
-        <v>3.42434289200739</v>
+        <v>3.662631181668157</v>
       </c>
       <c r="U87">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V87">
         <v>0.15</v>
       </c>
       <c r="W87">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y87">
-        <v>2.525250898493288</v>
+        <v>2.36747113980207</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1011645840798889</v>
+        <v>0.1012831295722886</v>
       </c>
       <c r="C88">
-        <v>3.603568687454725</v>
+        <v>3.180918894409608</v>
       </c>
       <c r="D88">
-        <v>35.14956868745472</v>
+        <v>35.10791889440961</v>
       </c>
       <c r="E88">
-        <v>20.866</v>
+        <v>21.247</v>
       </c>
       <c r="F88">
-        <v>32.766</v>
+        <v>33.147</v>
       </c>
       <c r="G88">
         <v>1.22</v>
@@ -8503,28 +8503,28 @@
         <v>5.88</v>
       </c>
       <c r="M88">
-        <v>2.4836628</v>
+        <v>2.5125426</v>
       </c>
       <c r="N88">
-        <v>3.3963372</v>
+        <v>3.3674574</v>
       </c>
       <c r="O88">
-        <v>0.5094505799999999</v>
+        <v>0.5051186099999999</v>
       </c>
       <c r="P88">
-        <v>2.88688662</v>
+        <v>2.86233879</v>
       </c>
       <c r="Q88">
-        <v>4.63688662</v>
+        <v>4.61233879</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3268198862849206</v>
+        <v>0.3479156120945279</v>
       </c>
       <c r="T88">
-        <v>3.662631181668157</v>
+        <v>3.937579208199812</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.36747113980207</v>
+        <v>2.340258827850322</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1012831295722886</v>
+        <v>0.1014016750646884</v>
       </c>
       <c r="C89">
-        <v>3.180918894409608</v>
+        <v>2.758367688758476</v>
       </c>
       <c r="D89">
-        <v>35.10791889440961</v>
+        <v>35.06636768875848</v>
       </c>
       <c r="E89">
-        <v>21.247</v>
+        <v>21.628</v>
       </c>
       <c r="F89">
-        <v>33.147</v>
+        <v>33.528</v>
       </c>
       <c r="G89">
         <v>1.22</v>
@@ -8585,28 +8585,28 @@
         <v>5.88</v>
       </c>
       <c r="M89">
-        <v>2.5125426</v>
+        <v>2.5414224</v>
       </c>
       <c r="N89">
-        <v>3.3674574</v>
+        <v>3.3385776</v>
       </c>
       <c r="O89">
-        <v>0.5051186099999999</v>
+        <v>0.5007866399999999</v>
       </c>
       <c r="P89">
-        <v>2.86233879</v>
+        <v>2.83779096</v>
       </c>
       <c r="Q89">
-        <v>4.61233879</v>
+        <v>4.58779096</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3479156120945279</v>
+        <v>0.3725272922057363</v>
       </c>
       <c r="T89">
-        <v>3.937579208199812</v>
+        <v>4.258351905820078</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.340258827850322</v>
+        <v>2.313664977533841</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1014016750646884</v>
+        <v>0.1015202205570881</v>
       </c>
       <c r="C90">
-        <v>2.758367688758476</v>
+        <v>2.33591472087231</v>
       </c>
       <c r="D90">
-        <v>35.06636768875848</v>
+        <v>35.02491472087231</v>
       </c>
       <c r="E90">
-        <v>21.628</v>
+        <v>22.009</v>
       </c>
       <c r="F90">
-        <v>33.528</v>
+        <v>33.909</v>
       </c>
       <c r="G90">
         <v>1.22</v>
@@ -8667,28 +8667,28 @@
         <v>5.88</v>
       </c>
       <c r="M90">
-        <v>2.5414224</v>
+        <v>2.5703022</v>
       </c>
       <c r="N90">
-        <v>3.3385776</v>
+        <v>3.3096978</v>
       </c>
       <c r="O90">
-        <v>0.5007866399999999</v>
+        <v>0.49645467</v>
       </c>
       <c r="P90">
-        <v>2.83779096</v>
+        <v>2.81324313</v>
       </c>
       <c r="Q90">
-        <v>4.58779096</v>
+        <v>4.56324313</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3725272922057363</v>
+        <v>0.4016138232462554</v>
       </c>
       <c r="T90">
-        <v>4.258351905820078</v>
+        <v>4.637446912098572</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.313664977533841</v>
+        <v>2.287668741831213</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1015202205570881</v>
+        <v>0.1016387660494878</v>
       </c>
       <c r="C91">
-        <v>2.33591472087231</v>
+        <v>1.913559642773336</v>
       </c>
       <c r="D91">
-        <v>35.02491472087231</v>
+        <v>34.98355964277334</v>
       </c>
       <c r="E91">
-        <v>22.009</v>
+        <v>22.39</v>
       </c>
       <c r="F91">
-        <v>33.909</v>
+        <v>34.29</v>
       </c>
       <c r="G91">
         <v>1.22</v>
@@ -8749,28 +8749,28 @@
         <v>5.88</v>
       </c>
       <c r="M91">
-        <v>2.5703022</v>
+        <v>2.599182</v>
       </c>
       <c r="N91">
-        <v>3.3096978</v>
+        <v>3.280818</v>
       </c>
       <c r="O91">
-        <v>0.49645467</v>
+        <v>0.4921226999999999</v>
       </c>
       <c r="P91">
-        <v>2.81324313</v>
+        <v>2.7886953</v>
       </c>
       <c r="Q91">
-        <v>4.56324313</v>
+        <v>4.5386953</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4016138232462554</v>
+        <v>0.4365176604948783</v>
       </c>
       <c r="T91">
-        <v>4.637446912098572</v>
+        <v>5.092360919632767</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.287668741831213</v>
+        <v>2.262250200255311</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1016387660494878</v>
+        <v>0.1017573115418876</v>
       </c>
       <c r="C92">
-        <v>1.913559642773336</v>
+        <v>1.491302108125346</v>
       </c>
       <c r="D92">
-        <v>34.98355964277334</v>
+        <v>34.94230210812535</v>
       </c>
       <c r="E92">
-        <v>22.39</v>
+        <v>22.771</v>
       </c>
       <c r="F92">
-        <v>34.29</v>
+        <v>34.671</v>
       </c>
       <c r="G92">
         <v>1.22</v>
@@ -8831,28 +8831,28 @@
         <v>5.88</v>
       </c>
       <c r="M92">
-        <v>2.599182</v>
+        <v>2.6280618</v>
       </c>
       <c r="N92">
-        <v>3.280818</v>
+        <v>3.2519382</v>
       </c>
       <c r="O92">
-        <v>0.4921226999999999</v>
+        <v>0.48779073</v>
       </c>
       <c r="P92">
-        <v>2.7886953</v>
+        <v>2.76414747</v>
       </c>
       <c r="Q92">
-        <v>4.5386953</v>
+        <v>4.514147469999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4365176604948783</v>
+        <v>0.4791779060209729</v>
       </c>
       <c r="T92">
-        <v>5.092360919632767</v>
+        <v>5.648366928841225</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.262250200255311</v>
+        <v>2.237390307944813</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1017573115418876</v>
+        <v>0.1018758570342873</v>
       </c>
       <c r="C93">
-        <v>1.491302108125346</v>
+        <v>1.069141772223986</v>
       </c>
       <c r="D93">
-        <v>34.94230210812535</v>
+        <v>34.90114177222399</v>
       </c>
       <c r="E93">
-        <v>22.771</v>
+        <v>23.152</v>
       </c>
       <c r="F93">
-        <v>34.671</v>
+        <v>35.052</v>
       </c>
       <c r="G93">
         <v>1.22</v>
@@ -8913,28 +8913,28 @@
         <v>5.88</v>
       </c>
       <c r="M93">
-        <v>2.6280618</v>
+        <v>2.6569416</v>
       </c>
       <c r="N93">
-        <v>3.2519382</v>
+        <v>3.2230584</v>
       </c>
       <c r="O93">
-        <v>0.48779073</v>
+        <v>0.4834587599999999</v>
       </c>
       <c r="P93">
-        <v>2.76414747</v>
+        <v>2.73959964</v>
       </c>
       <c r="Q93">
-        <v>4.514147469999999</v>
+        <v>4.48959964</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4791779060209729</v>
+        <v>0.5325032129285913</v>
       </c>
       <c r="T93">
-        <v>5.648366928841225</v>
+        <v>6.343374440351801</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.237390307944813</v>
+        <v>2.213070848075848</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1018758570342873</v>
+        <v>0.101994402526687</v>
       </c>
       <c r="C94">
-        <v>1.069141772223986</v>
+        <v>0.6470782919871567</v>
       </c>
       <c r="D94">
-        <v>34.90114177222399</v>
+        <v>34.86007829198716</v>
       </c>
       <c r="E94">
-        <v>23.152</v>
+        <v>23.533</v>
       </c>
       <c r="F94">
-        <v>35.052</v>
+        <v>35.433</v>
       </c>
       <c r="G94">
         <v>1.22</v>
@@ -8995,28 +8995,28 @@
         <v>5.88</v>
       </c>
       <c r="M94">
-        <v>2.6569416</v>
+        <v>2.6858214</v>
       </c>
       <c r="N94">
-        <v>3.2230584</v>
+        <v>3.1941786</v>
       </c>
       <c r="O94">
-        <v>0.4834587599999999</v>
+        <v>0.47912679</v>
       </c>
       <c r="P94">
-        <v>2.73959964</v>
+        <v>2.71505181</v>
       </c>
       <c r="Q94">
-        <v>4.48959964</v>
+        <v>4.46505181</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5325032129285913</v>
+        <v>0.6010643218098148</v>
       </c>
       <c r="T94">
-        <v>6.343374440351801</v>
+        <v>7.236955526579683</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.213070848075848</v>
+        <v>2.18927438734385</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.101994402526687</v>
+        <v>0.1021129480190867</v>
       </c>
       <c r="C95">
-        <v>0.6470782919871567</v>
+        <v>0.2251113259455337</v>
       </c>
       <c r="D95">
-        <v>34.86007829198716</v>
+        <v>34.81911132594553</v>
       </c>
       <c r="E95">
-        <v>23.533</v>
+        <v>23.914</v>
       </c>
       <c r="F95">
-        <v>35.433</v>
+        <v>35.814</v>
       </c>
       <c r="G95">
         <v>1.22</v>
@@ -9077,28 +9077,28 @@
         <v>5.88</v>
       </c>
       <c r="M95">
-        <v>2.6858214</v>
+        <v>2.7147012</v>
       </c>
       <c r="N95">
-        <v>3.1941786</v>
+        <v>3.1652988</v>
       </c>
       <c r="O95">
-        <v>0.47912679</v>
+        <v>0.4747948199999999</v>
       </c>
       <c r="P95">
-        <v>2.71505181</v>
+        <v>2.690503979999999</v>
       </c>
       <c r="Q95">
-        <v>4.46505181</v>
+        <v>4.440503979999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6010643218098148</v>
+        <v>0.6924791336514463</v>
       </c>
       <c r="T95">
-        <v>7.236955526579683</v>
+        <v>8.428396974883524</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.18927438734385</v>
+        <v>2.165984234286999</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1021129480190867</v>
+        <v>0.1022314935114865</v>
       </c>
       <c r="C96">
-        <v>0.2251113259455337</v>
+        <v>-0.1967594657669807</v>
       </c>
       <c r="D96">
-        <v>34.81911132594553</v>
+        <v>34.77824053423303</v>
       </c>
       <c r="E96">
-        <v>23.914</v>
+        <v>24.29500000000001</v>
       </c>
       <c r="F96">
-        <v>35.814</v>
+        <v>36.19500000000001</v>
       </c>
       <c r="G96">
         <v>1.22</v>
@@ -9159,28 +9159,28 @@
         <v>5.88</v>
       </c>
       <c r="M96">
-        <v>2.7147012</v>
+        <v>2.743581000000001</v>
       </c>
       <c r="N96">
-        <v>3.1652988</v>
+        <v>3.136418999999999</v>
       </c>
       <c r="O96">
-        <v>0.4747948199999999</v>
+        <v>0.4704628499999999</v>
       </c>
       <c r="P96">
-        <v>2.690503979999999</v>
+        <v>2.66595615</v>
       </c>
       <c r="Q96">
-        <v>4.440503979999999</v>
+        <v>4.41595615</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6924791336514463</v>
+        <v>0.8204598702297307</v>
       </c>
       <c r="T96">
-        <v>8.428396974883524</v>
+        <v>10.09641500250891</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.165984234286999</v>
+        <v>2.143184400241873</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1022314935114865</v>
+        <v>0.1023500390038862</v>
       </c>
       <c r="C97">
-        <v>-0.1967594657669807</v>
+        <v>-0.6185344214225665</v>
       </c>
       <c r="D97">
-        <v>34.77824053423303</v>
+        <v>34.73746557857744</v>
       </c>
       <c r="E97">
-        <v>24.29500000000001</v>
+        <v>24.67600000000001</v>
       </c>
       <c r="F97">
-        <v>36.19500000000001</v>
+        <v>36.57600000000001</v>
       </c>
       <c r="G97">
         <v>1.22</v>
@@ -9241,28 +9241,28 @@
         <v>5.88</v>
       </c>
       <c r="M97">
-        <v>2.743581000000001</v>
+        <v>2.772460800000001</v>
       </c>
       <c r="N97">
-        <v>3.136418999999999</v>
+        <v>3.107539199999999</v>
       </c>
       <c r="O97">
-        <v>0.4704628499999999</v>
+        <v>0.4661308799999999</v>
       </c>
       <c r="P97">
-        <v>2.66595615</v>
+        <v>2.64140832</v>
       </c>
       <c r="Q97">
-        <v>4.41595615</v>
+        <v>4.39140832</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8204598702297307</v>
+        <v>1.012430975097157</v>
       </c>
       <c r="T97">
-        <v>10.09641500250891</v>
+        <v>12.59844204394698</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.143184400241873</v>
+        <v>2.120859562739354</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1023500390038862</v>
+        <v>0.1024685844962859</v>
       </c>
       <c r="C98">
-        <v>-0.6185344214225594</v>
+        <v>-1.040213877708894</v>
       </c>
       <c r="D98">
-        <v>34.73746557857744</v>
+        <v>34.69678612229111</v>
       </c>
       <c r="E98">
-        <v>24.676</v>
+        <v>25.057</v>
       </c>
       <c r="F98">
-        <v>36.576</v>
+        <v>36.957</v>
       </c>
       <c r="G98">
         <v>1.22</v>
@@ -9323,28 +9323,28 @@
         <v>5.88</v>
       </c>
       <c r="M98">
-        <v>2.7724608</v>
+        <v>2.8013406</v>
       </c>
       <c r="N98">
-        <v>3.1075392</v>
+        <v>3.0786594</v>
       </c>
       <c r="O98">
-        <v>0.4661308799999999</v>
+        <v>0.46179891</v>
       </c>
       <c r="P98">
-        <v>2.64140832</v>
+        <v>2.61686049</v>
       </c>
       <c r="Q98">
-        <v>4.39140832</v>
+        <v>4.36686049</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.012430975097155</v>
+        <v>1.332382816542864</v>
       </c>
       <c r="T98">
-        <v>12.59844204394695</v>
+        <v>16.76848711301038</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.120859562739354</v>
+        <v>2.098995031164722</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1024685844962859</v>
+        <v>0.1025871299886857</v>
       </c>
       <c r="C99">
-        <v>-1.040213877708894</v>
+        <v>-1.461798169738358</v>
       </c>
       <c r="D99">
-        <v>34.69678612229111</v>
+        <v>34.65620183026164</v>
       </c>
       <c r="E99">
-        <v>25.057</v>
+        <v>25.438</v>
       </c>
       <c r="F99">
-        <v>36.957</v>
+        <v>37.338</v>
       </c>
       <c r="G99">
         <v>1.22</v>
@@ -9405,28 +9405,28 @@
         <v>5.88</v>
       </c>
       <c r="M99">
-        <v>2.8013406</v>
+        <v>2.8302204</v>
       </c>
       <c r="N99">
-        <v>3.0786594</v>
+        <v>3.049779599999999</v>
       </c>
       <c r="O99">
-        <v>0.46179891</v>
+        <v>0.4574669399999999</v>
       </c>
       <c r="P99">
-        <v>2.61686049</v>
+        <v>2.59231266</v>
       </c>
       <c r="Q99">
-        <v>4.36686049</v>
+        <v>4.342312659999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.332382816542864</v>
+        <v>1.972286499434282</v>
       </c>
       <c r="T99">
-        <v>16.76848711301038</v>
+        <v>25.10857725113726</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.098995031164722</v>
+        <v>2.077576714520183</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1025871299886857</v>
+        <v>0.1027056754810854</v>
       </c>
       <c r="C100">
-        <v>-1.461798169738358</v>
+        <v>-1.883287631057257</v>
       </c>
       <c r="D100">
-        <v>34.65620183026164</v>
+        <v>34.61571236894275</v>
       </c>
       <c r="E100">
-        <v>25.438</v>
+        <v>25.819</v>
       </c>
       <c r="F100">
-        <v>37.338</v>
+        <v>37.719</v>
       </c>
       <c r="G100">
         <v>1.22</v>
@@ -9487,28 +9487,28 @@
         <v>5.88</v>
       </c>
       <c r="M100">
-        <v>2.8302204</v>
+        <v>2.8591002</v>
       </c>
       <c r="N100">
-        <v>3.049779599999999</v>
+        <v>3.0208998</v>
       </c>
       <c r="O100">
-        <v>0.4574669399999999</v>
+        <v>0.4531349699999999</v>
       </c>
       <c r="P100">
-        <v>2.59231266</v>
+        <v>2.56776483</v>
       </c>
       <c r="Q100">
-        <v>4.342312659999999</v>
+        <v>4.31776483</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.972286499434282</v>
+        <v>3.891997548108537</v>
       </c>
       <c r="T100">
-        <v>25.10857725113726</v>
+        <v>50.12884766551787</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.077576714520183</v>
+        <v>2.056591091141192</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1027056754810854</v>
-      </c>
-      <c r="C101">
-        <v>-1.883287631057257</v>
-      </c>
-      <c r="D101">
-        <v>34.61571236894275</v>
-      </c>
-      <c r="E101">
-        <v>25.819</v>
-      </c>
-      <c r="F101">
-        <v>37.719</v>
-      </c>
-      <c r="G101">
-        <v>1.22</v>
-      </c>
-      <c r="H101">
-        <v>26.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>7.63</v>
-      </c>
-      <c r="K101">
-        <v>1.75</v>
-      </c>
-      <c r="L101">
-        <v>5.88</v>
-      </c>
-      <c r="M101">
-        <v>2.8591002</v>
-      </c>
-      <c r="N101">
-        <v>3.0208998</v>
-      </c>
-      <c r="O101">
-        <v>0.4531349699999999</v>
-      </c>
-      <c r="P101">
-        <v>2.56776483</v>
-      </c>
-      <c r="Q101">
-        <v>4.31776483</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.891997548108537</v>
-      </c>
-      <c r="T101">
-        <v>50.12884766551787</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.06443</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.056591091141192</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
